--- a/livrables/RS_2026-2027_Octobre_seul.xlsx
+++ b/livrables/RS_2026-2027_Octobre_seul.xlsx
@@ -14,13 +14,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'S4 05-11 oct'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'S4 05-11 oct'!$A$1:$H$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'S4 05-11 oct'!$A$1:$H$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'S5 12-18 oct'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'S5 12-18 oct'!$A$1:$H$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'S5 12-18 oct'!$A$1:$H$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'S6 19-25 oct'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'S6 19-25 oct'!$A$1:$H$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'S6 19-25 oct'!$A$1:$H$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'S7 26 oct-01 nov'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'S7 26 oct-01 nov'!$A$1:$H$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'S7 26 oct-01 nov'!$A$1:$H$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -690,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -720,7 +720,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Chaque case = une séance : 1re ligne l’horaire, 2e la matière, 3e l’enseignant.   La couleur indique la famille de matières.   ◆ Q-A / ◆ Q-B = séance par quinzaine.   Case grise = aucune séance.   Contenu figé.</t>
+          <t>Une case = une séance : horaire / matière / enseignant.   Couleur = famille de matières.   ◆ Q-A ou Q-B = une semaine sur deux.   ⊕ = séance partagée.   ◆ OPTION = cours au choix.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -917,7 +917,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="52.59999999999999" customHeight="1">
+    <row r="8" ht="83" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>6éme Pilote (A)</t>
@@ -943,7 +943,8 @@
         <is>
           <t>19:30 - 21:00
 إيقاظ علمي
-Noura</t>
+Noura
+⊕ 6éme Pilote (A) + 6éme (B)</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -955,7 +956,7 @@
       </c>
       <c r="H8" s="11" t="n"/>
     </row>
-    <row r="9" ht="52.59999999999999" customHeight="1">
+    <row r="9" ht="83" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>6éme (B)</t>
@@ -977,7 +978,14 @@
 Noura</t>
         </is>
       </c>
-      <c r="F9" s="10" t="n"/>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+إيقاظ علمي
+Noura
+⊕ 6éme Pilote (A) + 6éme (B)</t>
+        </is>
+      </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
           <t>17:00 - 19:00
@@ -1001,7 +1009,7 @@
       <c r="G10" s="13" t="n"/>
       <c r="H10" s="13" t="n"/>
     </row>
-    <row r="11" ht="52.59999999999999" customHeight="1">
+    <row r="11" ht="67.8" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
           <t>7éme (A)</t>
@@ -1013,7 +1021,8 @@
         <is>
           <t>19:30 - 21:00
 فيزياء
-Melek</t>
+Melek
+⊕ 7éme (A) + 7éme (B)</t>
         </is>
       </c>
       <c r="E11" s="10" t="n"/>
@@ -1039,7 +1048,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="52.59999999999999" customHeight="1">
+    <row r="12" ht="67.8" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
           <t>7éme (B)</t>
@@ -1059,7 +1068,14 @@
 Imen Ben Lazrak</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n"/>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 7éme (A) + 7éme (B)</t>
+        </is>
+      </c>
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1083,7 +1099,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="52.59999999999999" customHeight="1">
+    <row r="13" ht="83" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
           <t>8éme (A)</t>
@@ -1109,7 +1125,8 @@
         <is>
           <t>19:30 - 21:00
 فيزياء
-Melek</t>
+Melek
+⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -1127,7 +1144,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="52.59999999999999" customHeight="1">
+    <row r="14" ht="83" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
         <is>
           <t>8éme (B)</t>
@@ -1138,7 +1155,8 @@
         <is>
           <t>19:30 - 21:00
 Arabe
-Yahya</t>
+Yahya
+⊕ 8éme (B) + 8éme (C)</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
@@ -1149,12 +1167,20 @@
         </is>
       </c>
       <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
+        </is>
+      </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
           <t>17:30 - 19:00   ◆ Q-B
 SVT
-Sabrine</t>
+Sabrine
+⊕ 8éme (B) + 8éme (C)</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
@@ -1165,14 +1191,21 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="52.59999999999999" customHeight="1">
+    <row r="15" ht="83" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
           <t>8éme (C)</t>
         </is>
       </c>
       <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+Arabe
+Yahya
+⊕ 8éme (B) + 8éme (C)</t>
+        </is>
+      </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
           <t>19:30 - 21:00
@@ -1187,11 +1220,25 @@
 Khouloud</t>
         </is>
       </c>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="11" t="n"/>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-B
+SVT
+Sabrine
+⊕ 8éme (B) + 8éme (C)</t>
+        </is>
+      </c>
       <c r="H15" s="11" t="n"/>
     </row>
-    <row r="16" ht="52.59999999999999" customHeight="1">
+    <row r="16" ht="83" customHeight="1">
       <c r="A16" s="14" t="inlineStr">
         <is>
           <t>9éme (A)</t>
@@ -1201,7 +1248,8 @@
         <is>
           <t>19:30 - 21:00
 فيزياء
-Melek</t>
+Melek
+⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -1251,13 +1299,20 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="52.59999999999999" customHeight="1">
+    <row r="18" ht="83" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
         <is>
           <t>9éme (B)</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
+        </is>
+      </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
           <t>19:15 - 20:45
@@ -1289,7 +1344,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="52.59999999999999" customHeight="1">
+    <row r="19" ht="67.8" customHeight="1">
       <c r="A19" s="15" t="n"/>
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="10" t="n"/>
@@ -1301,17 +1356,25 @@
         <is>
           <t>17:00 - 18:30
 Français
-Nassima</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="52.59999999999999" customHeight="1">
+Nassima
+⊕ 9éme (B) + 9éme (C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="83" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
         <is>
           <t>9éme (C)</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n"/>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
+        </is>
+      </c>
       <c r="C20" s="10" t="n"/>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -1341,7 +1404,14 @@
 Hajer</t>
         </is>
       </c>
-      <c r="H20" s="11" t="n"/>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>17:00 - 18:30
+Français
+Nassima
+⊕ 9éme (B) + 9éme (C)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
@@ -1455,7 +1525,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="52.59999999999999" customHeight="1">
+    <row r="25" ht="83" customHeight="1">
       <c r="A25" s="18" t="inlineStr">
         <is>
           <t>2éme Eco</t>
@@ -1466,7 +1536,8 @@
         <is>
           <t>19:30 - 21:00   ◆ Q-B
 Arabe
-Najet</t>
+Najet
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -1499,14 +1570,21 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="52.59999999999999" customHeight="1">
+    <row r="26" ht="83" customHeight="1">
       <c r="A26" s="18" t="inlineStr">
         <is>
           <t>2éme SCE</t>
         </is>
       </c>
       <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00   ◆ Q-B
+Arabe
+Najet
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
+        </is>
+      </c>
       <c r="D26" s="10" t="n"/>
       <c r="E26" s="10" t="inlineStr">
         <is>
@@ -1531,14 +1609,21 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="52.59999999999999" customHeight="1">
+    <row r="27" ht="83" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
         <is>
           <t>2éme INFO</t>
         </is>
       </c>
       <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00   ◆ Q-B
+Arabe
+Najet
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
+        </is>
+      </c>
       <c r="D27" s="10" t="n"/>
       <c r="E27" s="10" t="inlineStr">
         <is>
@@ -1563,7 +1648,7 @@
       </c>
       <c r="H27" s="11" t="n"/>
     </row>
-    <row r="28" ht="52.59999999999999" customHeight="1">
+    <row r="28" ht="98.19999999999999" customHeight="1">
       <c r="A28" s="18" t="inlineStr">
         <is>
           <t>3éme Eco</t>
@@ -1572,9 +1657,10 @@
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-B
+          <t>19:15 - 20:45   ◆ Q-B   ◆ OPTION
 Espagnol
-Imen</t>
+Imen
+⊕ 3éme Eco + 3éme INFO</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
@@ -1588,14 +1674,16 @@
         <is>
           <t>19:00 - 20:30   ◆ Q-B
 Philo
-Fayssel</t>
+Fayssel
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
           <t>17:30 - 19:00   ◆ Q-B
 Anglais
-Khaled</t>
+Khaled
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -1629,7 +1717,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="52.59999999999999" customHeight="1">
+    <row r="30" ht="98.19999999999999" customHeight="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
           <t>3éme INFO</t>
@@ -1644,9 +1732,10 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-B
-Italien
-Amel</t>
+          <t>19:15 - 20:45   ◆ Q-B   ◆ OPTION
+Espagnol
+Imen
+⊕ 3éme Eco + 3éme INFO</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
@@ -1656,8 +1745,22 @@
 Samia</t>
         </is>
       </c>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>19:00 - 20:30   ◆ Q-B
+Philo
+Fayssel
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-B
+Anglais
+Khaled
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
           <t>15:00 - 17:00
@@ -1673,31 +1776,69 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="52.59999999999999" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>3éme SCE</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>19:00 - 20:30
-Math
-Lotfi</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="n"/>
+    <row r="31" ht="98.19999999999999" customHeight="1">
+      <c r="A31" s="19" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>19:15 - 20:45   ◆ Q-B   ◆ OPTION
+Italien
+Amel
+⊕ 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
       <c r="D31" s="10" t="n"/>
       <c r="E31" s="10" t="n"/>
       <c r="F31" s="10" t="n"/>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
+    </row>
+    <row r="32" ht="98.19999999999999" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>3éme SCE</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>19:00 - 20:30
+Math
+Lotfi</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>19:15 - 20:45   ◆ Q-B   ◆ OPTION
+Italien
+Amel
+⊕ 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>19:00 - 20:30   ◆ Q-B
+Philo
+Fayssel
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-B
+Anglais
+Khaled
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>17:30 - 19:00
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>10:30 - 12:00
 Physique
@@ -1705,57 +1846,59 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="21" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
+    <row r="33" ht="21" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>CYCLE BAC   (3 classes)</t>
         </is>
       </c>
-      <c r="B32" s="21" t="n"/>
-      <c r="C32" s="21" t="n"/>
-      <c r="D32" s="21" t="n"/>
-      <c r="E32" s="21" t="n"/>
-      <c r="F32" s="21" t="n"/>
-      <c r="G32" s="21" t="n"/>
-      <c r="H32" s="21" t="n"/>
-    </row>
-    <row r="33" ht="52.59999999999999" customHeight="1">
-      <c r="A33" s="22" t="inlineStr">
+      <c r="B33" s="21" t="n"/>
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="21" t="n"/>
+      <c r="E33" s="21" t="n"/>
+      <c r="F33" s="21" t="n"/>
+      <c r="G33" s="21" t="n"/>
+      <c r="H33" s="21" t="n"/>
+    </row>
+    <row r="34" ht="83" customHeight="1">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>Bac Eco</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 Gestion
 Yassine</t>
         </is>
       </c>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>19:30 - 21:00   ◆ Q-B
 Arabe
-Najet</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
+Najet
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>17:30 - 19:00   ◆ Q-B
 Français
-Nabil</t>
-        </is>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
+Nabil
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>18:30 - 20:00   ◆ Q-B
 Géographie
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>10:30 - 12:00
 Math
@@ -1763,15 +1906,15 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="52.59999999999999" customHeight="1">
-      <c r="A34" s="23" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="11" t="n"/>
-      <c r="H34" s="11" t="inlineStr">
+    <row r="35" ht="52.59999999999999" customHeight="1">
+      <c r="A35" s="23" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>12:30 - 14:30
 Eco
@@ -1779,69 +1922,97 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="52.59999999999999" customHeight="1">
-      <c r="A35" s="22" t="inlineStr">
+    <row r="36" ht="83" customHeight="1">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>Bac SCE</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 Physique
 Sondes</t>
         </is>
       </c>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 Math
 Ahmed</t>
         </is>
       </c>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00   ◆ Q-B
+Arabe
+Najet
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-B
+Français
+Nabil
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>19:00 - 20:30
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H35" s="11" t="n"/>
-    </row>
-    <row r="36" ht="52.59999999999999" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="H36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="83" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>Bac INFO</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>19:30 - 21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00   ◆ Q-B
+Arabe
+Najet
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-B
+Français
+Nabil
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 ALGO
 Heni</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>15:30 - 17:00
 Math
@@ -1850,20 +2021,21 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A34:A35"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A33:A34"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A33:H33"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A32:H32"/>
     <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A30:A31"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:H36">
+  <conditionalFormatting sqref="B5:H37">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Arabe"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"عربية"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
@@ -1912,7 +2084,7 @@
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="9" min="0" max="16383" man="1"/>
     <brk id="20" min="0" max="16383" man="1"/>
-    <brk id="31" min="0" max="16383" man="1"/>
+    <brk id="32" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -1924,7 +2096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1954,7 +2126,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Chaque case = une séance : 1re ligne l’horaire, 2e la matière, 3e l’enseignant.   La couleur indique la famille de matières.   ◆ Q-A / ◆ Q-B = séance par quinzaine.   Case grise = aucune séance.   Contenu figé.</t>
+          <t>Une case = une séance : horaire / matière / enseignant.   Couleur = famille de matières.   ◆ Q-A ou Q-B = une semaine sur deux.   ⊕ = séance partagée.   ◆ OPTION = cours au choix.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2152,7 +2324,7 @@
       </c>
       <c r="H7" s="11" t="n"/>
     </row>
-    <row r="8" ht="52.59999999999999" customHeight="1">
+    <row r="8" ht="83" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>6éme Pilote (A)</t>
@@ -2178,7 +2350,8 @@
         <is>
           <t>19:30 - 21:00
 إيقاظ علمي
-Noura</t>
+Noura
+⊕ 6éme Pilote (A) + 6éme (B)</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -2192,7 +2365,8 @@
         <is>
           <t>12:00 - 13:30   ◆ Q-A
 Anglais
-Samar</t>
+Samar
+⊕ 6éme Pilote (A) + 6éme (B)</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2393,14 @@
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F9" s="10" t="n"/>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+إيقاظ علمي
+Noura
+⊕ 6éme Pilote (A) + 6éme (B)</t>
+        </is>
+      </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
           <t>17:00 - 19:00
@@ -2227,7 +2408,14 @@
 Lobna</t>
         </is>
       </c>
-      <c r="H9" s="11" t="n"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>12:00 - 13:30   ◆ Q-A
+Anglais
+Samar
+⊕ 6éme Pilote (A) + 6éme (B)</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -2243,7 +2431,7 @@
       <c r="G10" s="13" t="n"/>
       <c r="H10" s="13" t="n"/>
     </row>
-    <row r="11" ht="52.59999999999999" customHeight="1">
+    <row r="11" ht="67.8" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
           <t>7éme (A)</t>
@@ -2261,7 +2449,8 @@
         <is>
           <t>19:30 - 21:00
 فيزياء
-Melek</t>
+Melek
+⊕ 7éme (A) + 7éme (B)</t>
         </is>
       </c>
       <c r="E11" s="10" t="n"/>
@@ -2303,7 +2492,7 @@
       </c>
       <c r="H12" s="11" t="n"/>
     </row>
-    <row r="13" ht="52.59999999999999" customHeight="1">
+    <row r="13" ht="67.8" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
           <t>7éme (B)</t>
@@ -2317,7 +2506,14 @@
         </is>
       </c>
       <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 7éme (A) + 7éme (B)</t>
+        </is>
+      </c>
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -2362,7 +2558,8 @@
         <is>
           <t>19:30 - 21:00
 فيزياء
-Melek</t>
+Melek
+⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -2380,7 +2577,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="52.59999999999999" customHeight="1">
+    <row r="15" ht="83" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
           <t>8éme (B)</t>
@@ -2391,7 +2588,8 @@
         <is>
           <t>19:30 - 21:00
 Arabe
-Yahya</t>
+Yahya
+⊕ 8éme (B) + 8éme (C)</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -2402,12 +2600,20 @@
         </is>
       </c>
       <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
+        </is>
+      </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
           <t>17:30 - 19:00   ◆ Q-A
 Anglais
-Imen Ben Lazrak</t>
+Imen Ben Lazrak
+⊕ 8éme (B) + 8éme (C)</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -2425,7 +2631,14 @@
         </is>
       </c>
       <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+Arabe
+Yahya
+⊕ 8éme (B) + 8éme (C)</t>
+        </is>
+      </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
           <t>19:30 - 21:00
@@ -2441,8 +2654,22 @@
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-A
+Anglais
+Imen Ben Lazrak
+⊕ 8éme (B) + 8éme (C)</t>
+        </is>
+      </c>
       <c r="H16" s="11" t="n"/>
     </row>
     <row r="17" ht="83" customHeight="1">
@@ -2455,7 +2682,8 @@
         <is>
           <t>19:30 - 21:00
 فيزياء
-Melek</t>
+Melek
+⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -2506,13 +2734,20 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="52.59999999999999" customHeight="1">
+    <row r="19" ht="83" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
         <is>
           <t>9éme (B)</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n"/>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
+        </is>
+      </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
           <t>19:15 - 20:45
@@ -2544,7 +2779,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="52.59999999999999" customHeight="1">
+    <row r="20" ht="67.8" customHeight="1">
       <c r="A20" s="15" t="n"/>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="10" t="n"/>
@@ -2556,7 +2791,8 @@
         <is>
           <t>17:00 - 18:30
 Français
-Nassima</t>
+Nassima
+⊕ 9éme (B) + 9éme (C)</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2802,14 @@
           <t>9éme (C)</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n"/>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
+        </is>
+      </c>
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="10" t="inlineStr">
         <is>
@@ -2597,7 +2840,14 @@
 Hajer</t>
         </is>
       </c>
-      <c r="H21" s="11" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>17:00 - 18:30
+Français
+Nassima
+⊕ 9éme (B) + 9éme (C)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
@@ -2723,7 +2973,8 @@
         <is>
           <t>19:15 - 20:45   ◆ Q-A
 Anglais
-Imen Bennour</t>
+Imen Bennour
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
@@ -2745,7 +2996,8 @@
         <is>
           <t>17:30 - 19:00   ◆ Q-A
 Français
-Nabil</t>
+Nabil
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -2770,7 +3022,14 @@
         </is>
       </c>
       <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>19:15 - 20:45   ◆ Q-A
+Anglais
+Imen Bennour
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
+        </is>
+      </c>
       <c r="D27" s="10" t="n"/>
       <c r="E27" s="10" t="inlineStr">
         <is>
@@ -2780,7 +3039,14 @@
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F27" s="10" t="n"/>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-A
+Français
+Nabil
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
+        </is>
+      </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
           <t>16:00 - 17:30
@@ -2803,7 +3069,14 @@
         </is>
       </c>
       <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>19:15 - 20:45   ◆ Q-A
+Anglais
+Imen Bennour
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
+        </is>
+      </c>
       <c r="D28" s="10" t="n"/>
       <c r="E28" s="10" t="inlineStr">
         <is>
@@ -2815,9 +3088,10 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
-Math
-Haythem</t>
+          <t>17:30 - 19:00   ◆ Q-A
+Français
+Nabil
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -2829,44 +3103,62 @@
       </c>
       <c r="H28" s="11" t="n"/>
     </row>
-    <row r="29" ht="83" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>3éme Eco</t>
-        </is>
-      </c>
+    <row r="29" ht="52.59999999999999" customHeight="1">
+      <c r="A29" s="19" t="n"/>
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+Math
+Haythem</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="113.4" customHeight="1">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>3éme Eco</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>19:00 - 20:30
 Gestion
 Yassine</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>19:30 - 21:00   ◆ Q-A
 Arabe
 Najet
+⊕ 3éme Eco + 3éme INFO + 3éme SCE
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>19:00 - 20:30   ◆ Q-A
 Français
-Nabil</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
+Nabil
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>17:00 - 18:30   ◆ Q-A
 Histoire
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>10:30 - 12:00
 Eco
@@ -2874,15 +3166,15 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="52.59999999999999" customHeight="1">
-      <c r="A30" s="19" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="11" t="inlineStr">
+    <row r="31" ht="52.59999999999999" customHeight="1">
+      <c r="A31" s="19" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>14:00 - 15:30
 Math
@@ -2890,37 +3182,52 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="52.59999999999999" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="32" ht="113.4" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>3éme INFO</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>15:30 - 17:30
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>19:30 - 21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00   ◆ Q-A
+Arabe
+Najet
+⊕ 3éme Eco + 3éme INFO + 3éme SCE
+Jour férié (Évacuation) — à confirmer</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>19:00 - 20:30   ◆ Q-A
+Français
+Nabil
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>15:00 - 17:00
 ALGO
 Aymen</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>12:00 - 13:30
 Math
@@ -2928,31 +3235,46 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="52.59999999999999" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="33" ht="113.4" customHeight="1">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>3éme SCE</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>19:00 - 20:30
 Math
 Lotfi</t>
         </is>
       </c>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00   ◆ Q-A
+Arabe
+Najet
+⊕ 3éme Eco + 3éme INFO + 3éme SCE
+Jour férié (Évacuation) — à confirmer</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>19:00 - 20:30   ◆ Q-A
+Français
+Nabil
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>17:30 - 19:00
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>10:30 - 12:00
 Physique
@@ -2960,64 +3282,67 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="21" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
+    <row r="34" ht="21" customHeight="1">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>CYCLE BAC   (3 classes)</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n"/>
-      <c r="C33" s="21" t="n"/>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="21" t="n"/>
-      <c r="F33" s="21" t="n"/>
-      <c r="G33" s="21" t="n"/>
-      <c r="H33" s="21" t="n"/>
-    </row>
-    <row r="34" ht="83" customHeight="1">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="B34" s="21" t="n"/>
+      <c r="C34" s="21" t="n"/>
+      <c r="D34" s="21" t="n"/>
+      <c r="E34" s="21" t="n"/>
+      <c r="F34" s="21" t="n"/>
+      <c r="G34" s="21" t="n"/>
+      <c r="H34" s="21" t="n"/>
+    </row>
+    <row r="35" ht="113.4" customHeight="1">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>Bac Eco</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 Gestion
 Yassine</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45   ◆ Q-A
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>19:15 - 20:45   ◆ Q-A   ◆ OPTION
 Espagnol
-Imen</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="inlineStr">
+Imen
+⊕ Bac Eco + Bac SCE</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>19:00 - 20:30   ◆ Q-A
 Philo
 Fayssel
+⊕ Bac Eco + Bac SCE + Bac INFO
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>17:30 - 19:00   ◆ Q-A
 Anglais
-Khaled</t>
-        </is>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
+Khaled
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>18:30 - 20:00   ◆ Q-A
 Histoire
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>10:30 - 12:00
 Math
@@ -3025,15 +3350,15 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="52.59999999999999" customHeight="1">
-      <c r="A35" s="23" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="11" t="inlineStr">
+    <row r="36" ht="52.59999999999999" customHeight="1">
+      <c r="A36" s="23" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>12:30 - 14:30
 Eco
@@ -3041,75 +3366,130 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="52.59999999999999" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
+    <row r="37" ht="113.4" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>Bac SCE</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 Physique
 Sondes</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45   ◆ Q-A
-Italien
-Amel</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>19:15 - 20:45   ◆ Q-A   ◆ OPTION
+Espagnol
+Imen
+⊕ Bac Eco + Bac SCE</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 Math
 Ahmed</t>
         </is>
       </c>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>19:00 - 20:30   ◆ Q-A
+Philo
+Fayssel
+⊕ Bac Eco + Bac SCE + Bac INFO
+Jour férié (Évacuation) — à confirmer</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-A
+Anglais
+Khaled
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>19:00 - 20:30
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H36" s="11" t="n"/>
-    </row>
-    <row r="37" ht="52.59999999999999" customHeight="1">
-      <c r="A37" s="22" t="inlineStr">
+      <c r="H37" s="11" t="n"/>
+    </row>
+    <row r="38" ht="83" customHeight="1">
+      <c r="A38" s="23" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>19:15 - 20:45   ◆ Q-A   ◆ OPTION
+Italien
+Amel
+⊕ Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="113.4" customHeight="1">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>Bac INFO</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>19:30 - 21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>19:15 - 20:45   ◆ Q-A   ◆ OPTION
+Italien
+Amel
+⊕ Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>19:00 - 20:30   ◆ Q-A
+Philo
+Fayssel
+⊕ Bac Eco + Bac SCE + Bac INFO
+Jour férié (Évacuation) — à confirmer</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-A
+Anglais
+Khaled
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 ALGO
 Heni</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>15:30 - 17:00
 Math
@@ -3118,21 +3498,23 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A35:A36"/>
     <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A28:A29"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A29:A30"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:H37">
+  <conditionalFormatting sqref="B5:H39">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Arabe"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"عربية"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
@@ -3181,7 +3563,7 @@
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="9" min="0" max="16383" man="1"/>
     <brk id="21" min="0" max="16383" man="1"/>
-    <brk id="32" min="0" max="16383" man="1"/>
+    <brk id="33" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -3193,7 +3575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3223,7 +3605,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Chaque case = une séance : 1re ligne l’horaire, 2e la matière, 3e l’enseignant.   La couleur indique la famille de matières.   ◆ Q-A / ◆ Q-B = séance par quinzaine.   Case grise = aucune séance.   Contenu figé.</t>
+          <t>Une case = une séance : horaire / matière / enseignant.   Couleur = famille de matières.   ◆ Q-A ou Q-B = une semaine sur deux.   ⊕ = séance partagée.   ◆ OPTION = cours au choix.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3420,7 +3802,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="52.59999999999999" customHeight="1">
+    <row r="8" ht="83" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>6éme Pilote (A)</t>
@@ -3446,7 +3828,8 @@
         <is>
           <t>19:30 - 21:00
 إيقاظ علمي
-Noura</t>
+Noura
+⊕ 6éme Pilote (A) + 6éme (B)</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -3458,7 +3841,7 @@
       </c>
       <c r="H8" s="11" t="n"/>
     </row>
-    <row r="9" ht="52.59999999999999" customHeight="1">
+    <row r="9" ht="83" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>6éme (B)</t>
@@ -3480,7 +3863,14 @@
 Noura</t>
         </is>
       </c>
-      <c r="F9" s="10" t="n"/>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+إيقاظ علمي
+Noura
+⊕ 6éme Pilote (A) + 6éme (B)</t>
+        </is>
+      </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
           <t>17:00 - 19:00
@@ -3504,7 +3894,7 @@
       <c r="G10" s="13" t="n"/>
       <c r="H10" s="13" t="n"/>
     </row>
-    <row r="11" ht="52.59999999999999" customHeight="1">
+    <row r="11" ht="67.8" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
           <t>7éme (A)</t>
@@ -3516,7 +3906,8 @@
         <is>
           <t>19:30 - 21:00
 فيزياء
-Melek</t>
+Melek
+⊕ 7éme (A) + 7éme (B)</t>
         </is>
       </c>
       <c r="E11" s="10" t="n"/>
@@ -3542,7 +3933,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="52.59999999999999" customHeight="1">
+    <row r="12" ht="67.8" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
           <t>7éme (B)</t>
@@ -3562,7 +3953,14 @@
 Imen Ben Lazrak</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n"/>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 7éme (A) + 7éme (B)</t>
+        </is>
+      </c>
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -3586,7 +3984,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="52.59999999999999" customHeight="1">
+    <row r="13" ht="83" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
           <t>8éme (A)</t>
@@ -3612,7 +4010,8 @@
         <is>
           <t>19:30 - 21:00
 فيزياء
-Melek</t>
+Melek
+⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -3630,7 +4029,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="52.59999999999999" customHeight="1">
+    <row r="14" ht="83" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
         <is>
           <t>8éme (B)</t>
@@ -3641,7 +4040,8 @@
         <is>
           <t>19:30 - 21:00
 Arabe
-Yahya</t>
+Yahya
+⊕ 8éme (B) + 8éme (C)</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
@@ -3652,12 +4052,20 @@
         </is>
       </c>
       <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
+        </is>
+      </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
           <t>17:30 - 19:00   ◆ Q-B
 SVT
-Sabrine</t>
+Sabrine
+⊕ 8éme (B) + 8éme (C)</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
@@ -3668,14 +4076,21 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="52.59999999999999" customHeight="1">
+    <row r="15" ht="83" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
           <t>8éme (C)</t>
         </is>
       </c>
       <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+Arabe
+Yahya
+⊕ 8éme (B) + 8éme (C)</t>
+        </is>
+      </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
           <t>19:30 - 21:00
@@ -3690,11 +4105,25 @@
 Khouloud</t>
         </is>
       </c>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="11" t="n"/>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-B
+SVT
+Sabrine
+⊕ 8éme (B) + 8éme (C)</t>
+        </is>
+      </c>
       <c r="H15" s="11" t="n"/>
     </row>
-    <row r="16" ht="52.59999999999999" customHeight="1">
+    <row r="16" ht="83" customHeight="1">
       <c r="A16" s="14" t="inlineStr">
         <is>
           <t>9éme (A)</t>
@@ -3704,7 +4133,8 @@
         <is>
           <t>19:30 - 21:00
 فيزياء
-Melek</t>
+Melek
+⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -3754,13 +4184,20 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="52.59999999999999" customHeight="1">
+    <row r="18" ht="83" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
         <is>
           <t>9éme (B)</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
+        </is>
+      </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
           <t>19:15 - 20:45
@@ -3792,7 +4229,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="52.59999999999999" customHeight="1">
+    <row r="19" ht="67.8" customHeight="1">
       <c r="A19" s="15" t="n"/>
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="10" t="n"/>
@@ -3804,17 +4241,25 @@
         <is>
           <t>17:00 - 18:30
 Français
-Nassima</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="52.59999999999999" customHeight="1">
+Nassima
+⊕ 9éme (B) + 9éme (C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="83" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
         <is>
           <t>9éme (C)</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n"/>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
+        </is>
+      </c>
       <c r="C20" s="10" t="n"/>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -3844,7 +4289,14 @@
 Hajer</t>
         </is>
       </c>
-      <c r="H20" s="11" t="n"/>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>17:00 - 18:30
+Français
+Nassima
+⊕ 9éme (B) + 9éme (C)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
@@ -3958,7 +4410,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="52.59999999999999" customHeight="1">
+    <row r="25" ht="83" customHeight="1">
       <c r="A25" s="18" t="inlineStr">
         <is>
           <t>2éme Eco</t>
@@ -3969,7 +4421,8 @@
         <is>
           <t>19:30 - 21:00   ◆ Q-B
 Arabe
-Najet</t>
+Najet
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -4002,14 +4455,21 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="52.59999999999999" customHeight="1">
+    <row r="26" ht="83" customHeight="1">
       <c r="A26" s="18" t="inlineStr">
         <is>
           <t>2éme SCE</t>
         </is>
       </c>
       <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00   ◆ Q-B
+Arabe
+Najet
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
+        </is>
+      </c>
       <c r="D26" s="10" t="n"/>
       <c r="E26" s="10" t="inlineStr">
         <is>
@@ -4034,14 +4494,21 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="52.59999999999999" customHeight="1">
+    <row r="27" ht="83" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
         <is>
           <t>2éme INFO</t>
         </is>
       </c>
       <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00   ◆ Q-B
+Arabe
+Najet
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
+        </is>
+      </c>
       <c r="D27" s="10" t="n"/>
       <c r="E27" s="10" t="inlineStr">
         <is>
@@ -4066,7 +4533,7 @@
       </c>
       <c r="H27" s="11" t="n"/>
     </row>
-    <row r="28" ht="52.59999999999999" customHeight="1">
+    <row r="28" ht="98.19999999999999" customHeight="1">
       <c r="A28" s="18" t="inlineStr">
         <is>
           <t>3éme Eco</t>
@@ -4075,9 +4542,10 @@
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-B
+          <t>19:15 - 20:45   ◆ Q-B   ◆ OPTION
 Espagnol
-Imen</t>
+Imen
+⊕ 3éme Eco + 3éme INFO</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
@@ -4091,14 +4559,16 @@
         <is>
           <t>19:00 - 20:30   ◆ Q-B
 Philo
-Fayssel</t>
+Fayssel
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
           <t>17:30 - 19:00   ◆ Q-B
 Anglais
-Khaled</t>
+Khaled
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -4132,7 +4602,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="52.59999999999999" customHeight="1">
+    <row r="30" ht="98.19999999999999" customHeight="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
           <t>3éme INFO</t>
@@ -4147,9 +4617,10 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-B
-Italien
-Amel</t>
+          <t>19:15 - 20:45   ◆ Q-B   ◆ OPTION
+Espagnol
+Imen
+⊕ 3éme Eco + 3éme INFO</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
@@ -4159,8 +4630,22 @@
 Samia</t>
         </is>
       </c>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>19:00 - 20:30   ◆ Q-B
+Philo
+Fayssel
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-B
+Anglais
+Khaled
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
           <t>15:00 - 17:00
@@ -4176,31 +4661,69 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="52.59999999999999" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>3éme SCE</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>19:00 - 20:30
-Math
-Lotfi</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="n"/>
+    <row r="31" ht="98.19999999999999" customHeight="1">
+      <c r="A31" s="19" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>19:15 - 20:45   ◆ Q-B   ◆ OPTION
+Italien
+Amel
+⊕ 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
       <c r="D31" s="10" t="n"/>
       <c r="E31" s="10" t="n"/>
       <c r="F31" s="10" t="n"/>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
+    </row>
+    <row r="32" ht="98.19999999999999" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>3éme SCE</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>19:00 - 20:30
+Math
+Lotfi</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>19:15 - 20:45   ◆ Q-B   ◆ OPTION
+Italien
+Amel
+⊕ 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>19:00 - 20:30   ◆ Q-B
+Philo
+Fayssel
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-B
+Anglais
+Khaled
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>17:30 - 19:00
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>10:30 - 12:00
 Physique
@@ -4208,57 +4731,59 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="21" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
+    <row r="33" ht="21" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>CYCLE BAC   (3 classes)</t>
         </is>
       </c>
-      <c r="B32" s="21" t="n"/>
-      <c r="C32" s="21" t="n"/>
-      <c r="D32" s="21" t="n"/>
-      <c r="E32" s="21" t="n"/>
-      <c r="F32" s="21" t="n"/>
-      <c r="G32" s="21" t="n"/>
-      <c r="H32" s="21" t="n"/>
-    </row>
-    <row r="33" ht="52.59999999999999" customHeight="1">
-      <c r="A33" s="22" t="inlineStr">
+      <c r="B33" s="21" t="n"/>
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="21" t="n"/>
+      <c r="E33" s="21" t="n"/>
+      <c r="F33" s="21" t="n"/>
+      <c r="G33" s="21" t="n"/>
+      <c r="H33" s="21" t="n"/>
+    </row>
+    <row r="34" ht="83" customHeight="1">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>Bac Eco</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 Gestion
 Yassine</t>
         </is>
       </c>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>19:30 - 21:00   ◆ Q-B
 Arabe
-Najet</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
+Najet
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>17:30 - 19:00   ◆ Q-B
 Français
-Nabil</t>
-        </is>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
+Nabil
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>18:30 - 20:00   ◆ Q-B
 Géographie
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>10:30 - 12:00
 Math
@@ -4266,15 +4791,15 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="52.59999999999999" customHeight="1">
-      <c r="A34" s="23" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="11" t="n"/>
-      <c r="H34" s="11" t="inlineStr">
+    <row r="35" ht="52.59999999999999" customHeight="1">
+      <c r="A35" s="23" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>12:30 - 14:30
 Eco
@@ -4282,69 +4807,97 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="52.59999999999999" customHeight="1">
-      <c r="A35" s="22" t="inlineStr">
+    <row r="36" ht="83" customHeight="1">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>Bac SCE</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 Physique
 Sondes</t>
         </is>
       </c>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 Math
 Ahmed</t>
         </is>
       </c>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00   ◆ Q-B
+Arabe
+Najet
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-B
+Français
+Nabil
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>19:00 - 20:30
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H35" s="11" t="n"/>
-    </row>
-    <row r="36" ht="52.59999999999999" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="H36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="83" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>Bac INFO</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>19:30 - 21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00   ◆ Q-B
+Arabe
+Najet
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-B
+Français
+Nabil
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 ALGO
 Heni</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>15:30 - 17:00
 Math
@@ -4353,20 +4906,21 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A34:A35"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A33:A34"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A33:H33"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A32:H32"/>
     <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A30:A31"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:H36">
+  <conditionalFormatting sqref="B5:H37">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Arabe"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"عربية"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
@@ -4415,7 +4969,7 @@
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="9" min="0" max="16383" man="1"/>
     <brk id="20" min="0" max="16383" man="1"/>
-    <brk id="31" min="0" max="16383" man="1"/>
+    <brk id="32" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -4427,7 +4981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4457,7 +5011,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Chaque case = une séance : 1re ligne l’horaire, 2e la matière, 3e l’enseignant.   La couleur indique la famille de matières.   ◆ Q-A / ◆ Q-B = séance par quinzaine.   Case grise = aucune séance.   Contenu figé.</t>
+          <t>Une case = une séance : horaire / matière / enseignant.   Couleur = famille de matières.   ◆ Q-A ou Q-B = une semaine sur deux.   ⊕ = séance partagée.   ◆ OPTION = cours au choix.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4654,7 +5208,7 @@
       </c>
       <c r="H7" s="11" t="n"/>
     </row>
-    <row r="8" ht="52.59999999999999" customHeight="1">
+    <row r="8" ht="83" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>6éme Pilote (A)</t>
@@ -4680,7 +5234,8 @@
         <is>
           <t>19:30 - 21:00
 إيقاظ علمي
-Noura</t>
+Noura
+⊕ 6éme Pilote (A) + 6éme (B)</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -4694,11 +5249,12 @@
         <is>
           <t>12:00 - 13:30   ◆ Q-A
 Anglais
-Samar</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="52.59999999999999" customHeight="1">
+Samar
+⊕ 6éme Pilote (A) + 6éme (B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="83" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>6éme (B)</t>
@@ -4720,7 +5276,14 @@
 Noura</t>
         </is>
       </c>
-      <c r="F9" s="10" t="n"/>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+إيقاظ علمي
+Noura
+⊕ 6éme Pilote (A) + 6éme (B)</t>
+        </is>
+      </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
           <t>17:00 - 19:00
@@ -4728,7 +5291,14 @@
 Lobna</t>
         </is>
       </c>
-      <c r="H9" s="11" t="n"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>12:00 - 13:30   ◆ Q-A
+Anglais
+Samar
+⊕ 6éme Pilote (A) + 6éme (B)</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -4744,7 +5314,7 @@
       <c r="G10" s="13" t="n"/>
       <c r="H10" s="13" t="n"/>
     </row>
-    <row r="11" ht="52.59999999999999" customHeight="1">
+    <row r="11" ht="67.8" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
           <t>7éme (A)</t>
@@ -4762,7 +5332,8 @@
         <is>
           <t>19:30 - 21:00
 فيزياء
-Melek</t>
+Melek
+⊕ 7éme (A) + 7éme (B)</t>
         </is>
       </c>
       <c r="E11" s="10" t="n"/>
@@ -4804,7 +5375,7 @@
       </c>
       <c r="H12" s="11" t="n"/>
     </row>
-    <row r="13" ht="52.59999999999999" customHeight="1">
+    <row r="13" ht="67.8" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
           <t>7éme (B)</t>
@@ -4818,7 +5389,14 @@
         </is>
       </c>
       <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 7éme (A) + 7éme (B)</t>
+        </is>
+      </c>
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -4836,7 +5414,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="52.59999999999999" customHeight="1">
+    <row r="14" ht="83" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
         <is>
           <t>8éme (A)</t>
@@ -4862,7 +5440,8 @@
         <is>
           <t>19:30 - 21:00
 فيزياء
-Melek</t>
+Melek
+⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -4880,7 +5459,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="52.59999999999999" customHeight="1">
+    <row r="15" ht="83" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
           <t>8éme (B)</t>
@@ -4891,7 +5470,8 @@
         <is>
           <t>19:30 - 21:00
 Arabe
-Yahya</t>
+Yahya
+⊕ 8éme (B) + 8éme (C)</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -4902,12 +5482,20 @@
         </is>
       </c>
       <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
+        </is>
+      </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
           <t>17:30 - 19:00   ◆ Q-A
 Anglais
-Imen Ben Lazrak</t>
+Imen Ben Lazrak
+⊕ 8éme (B) + 8éme (C)</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -4918,14 +5506,21 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="52.59999999999999" customHeight="1">
+    <row r="16" ht="83" customHeight="1">
       <c r="A16" s="14" t="inlineStr">
         <is>
           <t>8éme (C)</t>
         </is>
       </c>
       <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+Arabe
+Yahya
+⊕ 8éme (B) + 8éme (C)</t>
+        </is>
+      </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
           <t>19:30 - 21:00
@@ -4940,11 +5535,25 @@
 Khouloud</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-A
+Anglais
+Imen Ben Lazrak
+⊕ 8éme (B) + 8éme (C)</t>
+        </is>
+      </c>
       <c r="H16" s="11" t="n"/>
     </row>
-    <row r="17" ht="52.59999999999999" customHeight="1">
+    <row r="17" ht="83" customHeight="1">
       <c r="A17" s="14" t="inlineStr">
         <is>
           <t>9éme (A)</t>
@@ -4954,7 +5563,8 @@
         <is>
           <t>19:30 - 21:00
 فيزياء
-Melek</t>
+Melek
+⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -5004,13 +5614,20 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="52.59999999999999" customHeight="1">
+    <row r="19" ht="83" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
         <is>
           <t>9éme (B)</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n"/>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
+        </is>
+      </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
           <t>19:15 - 20:45
@@ -5042,7 +5659,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="52.59999999999999" customHeight="1">
+    <row r="20" ht="67.8" customHeight="1">
       <c r="A20" s="15" t="n"/>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="10" t="n"/>
@@ -5054,17 +5671,25 @@
         <is>
           <t>17:00 - 18:30
 Français
-Nassima</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="52.59999999999999" customHeight="1">
+Nassima
+⊕ 9éme (B) + 9éme (C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="83" customHeight="1">
       <c r="A21" s="14" t="inlineStr">
         <is>
           <t>9éme (C)</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n"/>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+فيزياء
+Melek
+⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
+        </is>
+      </c>
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="10" t="inlineStr">
         <is>
@@ -5094,7 +5719,14 @@
 Hajer</t>
         </is>
       </c>
-      <c r="H21" s="11" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>17:00 - 18:30
+Français
+Nassima
+⊕ 9éme (B) + 9éme (C)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
@@ -5208,7 +5840,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="52.59999999999999" customHeight="1">
+    <row r="26" ht="83" customHeight="1">
       <c r="A26" s="18" t="inlineStr">
         <is>
           <t>2éme Eco</t>
@@ -5219,7 +5851,8 @@
         <is>
           <t>19:15 - 20:45   ◆ Q-A
 Anglais
-Imen Bennour</t>
+Imen Bennour
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
@@ -5240,7 +5873,8 @@
         <is>
           <t>17:30 - 19:00   ◆ Q-A
 Français
-Nabil</t>
+Nabil
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -5258,14 +5892,21 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="52.59999999999999" customHeight="1">
+    <row r="27" ht="83" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
         <is>
           <t>2éme SCE</t>
         </is>
       </c>
       <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>19:15 - 20:45   ◆ Q-A
+Anglais
+Imen Bennour
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
+        </is>
+      </c>
       <c r="D27" s="10" t="n"/>
       <c r="E27" s="10" t="inlineStr">
         <is>
@@ -5274,7 +5915,14 @@
 Haythem</t>
         </is>
       </c>
-      <c r="F27" s="10" t="n"/>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-A
+Français
+Nabil
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
+        </is>
+      </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
           <t>16:00 - 17:30
@@ -5290,14 +5938,21 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="52.59999999999999" customHeight="1">
+    <row r="28" ht="83" customHeight="1">
       <c r="A28" s="18" t="inlineStr">
         <is>
           <t>2éme INFO</t>
         </is>
       </c>
       <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>19:15 - 20:45   ◆ Q-A
+Anglais
+Imen Bennour
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
+        </is>
+      </c>
       <c r="D28" s="10" t="n"/>
       <c r="E28" s="10" t="inlineStr">
         <is>
@@ -5308,9 +5963,10 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
-Math
-Haythem</t>
+          <t>17:30 - 19:00   ◆ Q-A
+Français
+Nabil
+⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -5323,42 +5979,60 @@
       <c r="H28" s="11" t="n"/>
     </row>
     <row r="29" ht="52.59999999999999" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>3éme Eco</t>
-        </is>
-      </c>
+      <c r="A29" s="19" t="n"/>
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00
+Math
+Haythem</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="83" customHeight="1">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>3éme Eco</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>19:00 - 20:30
 Gestion
 Yassine</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>19:30 - 21:00   ◆ Q-A
 Arabe
-Najet</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
+Najet
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>19:00 - 20:30   ◆ Q-A
 Français
-Nabil</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
+Nabil
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>17:00 - 18:30   ◆ Q-A
 Histoire
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>10:30 - 12:00
 Eco
@@ -5366,15 +6040,15 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="52.59999999999999" customHeight="1">
-      <c r="A30" s="19" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="11" t="inlineStr">
+    <row r="31" ht="52.59999999999999" customHeight="1">
+      <c r="A31" s="19" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>14:00 - 15:30
 Math
@@ -5382,37 +6056,51 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="52.59999999999999" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="32" ht="83" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>3éme INFO</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>15:30 - 17:30
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>19:30 - 21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00   ◆ Q-A
+Arabe
+Najet
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>19:00 - 20:30   ◆ Q-A
+Français
+Nabil
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>15:00 - 17:00
 ALGO
 Aymen</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>12:00 - 13:30
 Math
@@ -5420,31 +6108,45 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="52.59999999999999" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="33" ht="83" customHeight="1">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>3éme SCE</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>19:00 - 20:30
 Math
 Lotfi</t>
         </is>
       </c>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>19:30 - 21:00   ◆ Q-A
+Arabe
+Najet
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>19:00 - 20:30   ◆ Q-A
+Français
+Nabil
+⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>17:30 - 19:00
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>10:30 - 12:00
 Physique
@@ -5452,63 +6154,66 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="21" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
+    <row r="34" ht="21" customHeight="1">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>CYCLE BAC   (3 classes)</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n"/>
-      <c r="C33" s="21" t="n"/>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="21" t="n"/>
-      <c r="F33" s="21" t="n"/>
-      <c r="G33" s="21" t="n"/>
-      <c r="H33" s="21" t="n"/>
-    </row>
-    <row r="34" ht="52.59999999999999" customHeight="1">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="B34" s="21" t="n"/>
+      <c r="C34" s="21" t="n"/>
+      <c r="D34" s="21" t="n"/>
+      <c r="E34" s="21" t="n"/>
+      <c r="F34" s="21" t="n"/>
+      <c r="G34" s="21" t="n"/>
+      <c r="H34" s="21" t="n"/>
+    </row>
+    <row r="35" ht="83" customHeight="1">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>Bac Eco</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 Gestion
 Yassine</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45   ◆ Q-A
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>19:15 - 20:45   ◆ Q-A   ◆ OPTION
 Espagnol
-Imen</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="inlineStr">
+Imen
+⊕ Bac Eco + Bac SCE</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>19:00 - 20:30   ◆ Q-A
 Philo
-Fayssel</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
+Fayssel
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>17:30 - 19:00   ◆ Q-A
 Anglais
-Khaled</t>
-        </is>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
+Khaled
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>18:30 - 20:00   ◆ Q-A
 Histoire
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>10:30 - 12:00
 Math
@@ -5516,15 +6221,15 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="52.59999999999999" customHeight="1">
-      <c r="A35" s="23" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="11" t="inlineStr">
+    <row r="36" ht="52.59999999999999" customHeight="1">
+      <c r="A36" s="23" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>12:30 - 14:30
 Eco
@@ -5532,75 +6237,128 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="52.59999999999999" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
+    <row r="37" ht="83" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>Bac SCE</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 Physique
 Sondes</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45   ◆ Q-A
-Italien
-Amel</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>19:15 - 20:45   ◆ Q-A   ◆ OPTION
+Espagnol
+Imen
+⊕ Bac Eco + Bac SCE</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 Math
 Ahmed</t>
         </is>
       </c>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>19:00 - 20:30   ◆ Q-A
+Philo
+Fayssel
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-A
+Anglais
+Khaled
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>19:00 - 20:30
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H36" s="11" t="n"/>
-    </row>
-    <row r="37" ht="52.59999999999999" customHeight="1">
-      <c r="A37" s="22" t="inlineStr">
+      <c r="H37" s="11" t="n"/>
+    </row>
+    <row r="38" ht="83" customHeight="1">
+      <c r="A38" s="23" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>19:15 - 20:45   ◆ Q-A   ◆ OPTION
+Italien
+Amel
+⊕ Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="83" customHeight="1">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>Bac INFO</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>19:30 - 21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>19:15 - 20:45   ◆ Q-A   ◆ OPTION
+Italien
+Amel
+⊕ Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>19:00 - 20:30   ◆ Q-A
+Philo
+Fayssel
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>17:30 - 19:00   ◆ Q-A
+Anglais
+Khaled
+⊕ Bac Eco + Bac SCE + Bac INFO</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>19:00 - 21:00
 ALGO
 Heni</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>15:30 - 17:00
 Math
@@ -5609,21 +6367,23 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A35:A36"/>
     <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A28:A29"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A29:A30"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:H37">
+  <conditionalFormatting sqref="B5:H39">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Arabe"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"عربية"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
@@ -5672,7 +6432,7 @@
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="9" min="0" max="16383" man="1"/>
     <brk id="21" min="0" max="16383" man="1"/>
-    <brk id="32" min="0" max="16383" man="1"/>
+    <brk id="33" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/livrables/RS_2026-2027_Octobre_seul.xlsx
+++ b/livrables/RS_2026-2027_Octobre_seul.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,19 +57,14 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="001B2A41"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001B2A41"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="16">
@@ -101,11 +96,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003C6E91"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
@@ -116,7 +106,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF2F8"/>
+        <fgColor rgb="003C6E91"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,12 +116,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F3EF"/>
+        <fgColor rgb="009A6B1F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009A6B1F"/>
+        <fgColor rgb="005B4E8C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF2F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F3EF"/>
       </patternFill>
     </fill>
     <fill>
@@ -141,16 +141,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="005B4E8C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00EEEBF5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -186,6 +181,72 @@
         <color rgb="00DDE4EB"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B9C4D0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B9C4D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B9C4D0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B9C4D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B9C4D0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B9C4D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DDE4EB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DDE4EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DDE4EB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DDE4EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DDE4EB"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00DDE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -206,48 +267,48 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -303,22 +364,6 @@
           <fgColor rgb="00DCEFF2"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <b val="1"/>
-        <color rgb="00B03A2E"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <b val="1"/>
-        <color rgb="008A5A00"/>
-        <sz val="11"/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -690,17 +735,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -720,7 +765,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Une case = une séance : horaire / matière / enseignant.   Couleur = famille de matières.   ◆ Q-A ou Q-B = une semaine sur deux.   ⊕ = séance partagée.   ◆ OPTION = cours au choix.</t>
+          <t>Une case = une séance : horaire / matière / enseignant.   Couleur = famille de matières.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -780,53 +825,6 @@
         </is>
       </c>
     </row>
-    <row r="4" hidden="1" ht="3" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>__jour</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lundi</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Mardi</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Mercredi</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Jeudi</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Vendredi</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Samedi</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Dimanche</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-    </row>
     <row r="5" ht="21" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
@@ -841,7 +839,7 @@
       <c r="G5" s="8" t="n"/>
       <c r="H5" s="8" t="n"/>
     </row>
-    <row r="6" ht="52.59999999999999" customHeight="1">
+    <row r="6" ht="63" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>4éme</t>
@@ -849,7 +847,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 عربية
 Lobna</t>
         </is>
@@ -857,7 +855,7 @@
       <c r="C6" s="10" t="n"/>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 رياضيات
 Bassma</t>
         </is>
@@ -866,14 +864,14 @@
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>16:00 - 17:30
+          <t>16:00-17:30
 Français
 Hend</t>
         </is>
       </c>
       <c r="H6" s="11" t="n"/>
     </row>
-    <row r="7" ht="52.59999999999999" customHeight="1">
+    <row r="7" ht="63" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>5éme</t>
@@ -882,7 +880,7 @@
       <c r="B7" s="10" t="n"/>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 عربية
 Lobna</t>
         </is>
@@ -890,34 +888,34 @@
       <c r="D7" s="10" t="n"/>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 رياضيات
 Bassma</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30   ◆ Q-B
+          <t>19:00-20:30 Q-B
 إيقاظ علمي
 Bassma</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>18:00 - 19:30
+          <t>18:00-19:30
 Français
 Hend</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00   ◆ Q-B
+          <t>10:30-12:00 Q-B
 Anglais
 Samar</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="83" customHeight="1">
+    <row r="8" ht="63" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>6éme Pilote (A)</t>
@@ -925,7 +923,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Français
 Hend</t>
         </is>
@@ -933,7 +931,7 @@
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 رياضيات
 Noura</t>
         </is>
@@ -941,22 +939,21 @@
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 إيقاظ علمي
-Noura
-⊕ 6éme Pilote (A) + 6éme (B)</t>
+Noura</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 عربية
 Lobna</t>
         </is>
       </c>
       <c r="H8" s="11" t="n"/>
     </row>
-    <row r="9" ht="83" customHeight="1">
+    <row r="9" ht="63" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>6éme (B)</t>
@@ -965,7 +962,7 @@
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Français
 Hend</t>
         </is>
@@ -973,22 +970,15 @@
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 رياضيات
 Noura</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-إيقاظ علمي
-Noura
-⊕ 6éme Pilote (A) + 6éme (B)</t>
-        </is>
-      </c>
+      <c r="F9" s="12" t="n"/>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 19:00
+          <t>17:00-19:00
 عربية
 Lobna</t>
         </is>
@@ -996,21 +986,21 @@
       <c r="H9" s="11" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>CYCLE COLLÈGE   (8 classes)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="67.8" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="63" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>7éme (A)</t>
         </is>
@@ -1019,88 +1009,80 @@
       <c r="C11" s="10" t="n"/>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 فيزياء
-Melek
-⊕ 7éme (A) + 7éme (B)</t>
+Melek</t>
         </is>
       </c>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>18:00 - 19:30
+          <t>18:00-19:30
 Math
 Khouloud</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>18:00 - 19:30
+          <t>18:00-19:30
 Arabe
 Awatef</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>14:00 - 15:30
+          <t>14:00-15:30
 Français
 Marwa</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="67.8" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="12" ht="63" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>7éme (B)</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Arabe
 Yahya</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30   ◆ Q-B
+          <t>19:00-20:30 Q-B
 Anglais
 Imen Ben Lazrak</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 7éme (A) + 7éme (B)</t>
-        </is>
-      </c>
+      <c r="D12" s="12" t="n"/>
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Khouloud</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>16:00 - 17:30   ◆ Q-B
+          <t>16:00-17:30 Q-B
 SVT
 Sabrine</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>15:30 - 17:00
+          <t>15:30-17:00
 Français
 Marwa</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="83" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+    <row r="13" ht="63" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>8éme (A)</t>
         </is>
@@ -1109,43 +1091,42 @@
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Arabe
 Awatef</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Français
 Nassima</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 فيزياء
-Melek
-⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
+Melek</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>17:30 - 19:00   ◆ Q-B
+          <t>17:30-19:00 Q-B
 Anglais
 Imen Ben Lazrak</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>13:45 - 15:15
+          <t>13:45-15:15
 Math
 Hajer</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="83" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+    <row r="14" ht="63" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>8éme (B)</t>
         </is>
@@ -1153,108 +1134,77 @@
       <c r="B14" s="10" t="n"/>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Arabe
-Yahya
-⊕ 8éme (B) + 8éme (C)</t>
+Yahya</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Math
 Khouloud</t>
         </is>
       </c>
       <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>17:30-19:00 Q-B
+SVT
+Sabrine</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>17:00-18:30
+Français
+Marwa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="63" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>8éme (C)</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>19:30-21:00
+Français
+Nabil</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>19:15-20:45
+Math
+Khouloud</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="11" t="n"/>
+    </row>
+    <row r="16" ht="63" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>9éme (A)</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>19:30-21:00
 فيزياء
-Melek
-⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-B
-SVT
-Sabrine
-⊕ 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>17:00 - 18:30
-Français
-Marwa</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="83" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>8éme (C)</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-Arabe
-Yahya
-⊕ 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-Français
-Nabil</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45
-Math
-Khouloud</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-B
-SVT
-Sabrine
-⊕ 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="n"/>
-    </row>
-    <row r="16" ht="83" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>9éme (A)</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
+Melek</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Math
 Faouzi</t>
         </is>
@@ -1262,7 +1212,7 @@
       <c r="D16" s="10" t="n"/>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
@@ -1270,22 +1220,22 @@
       <c r="F16" s="10" t="n"/>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>16:30 - 18:00
+          <t>16:30-18:00
 Arabe
 Awatef</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Anglais
 Bassma</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="52.59999999999999" customHeight="1">
-      <c r="A17" s="15" t="n"/>
-      <c r="B17" s="10" t="n"/>
+    <row r="17" ht="63" customHeight="1">
+      <c r="A17" s="17" t="n"/>
+      <c r="B17" s="16" t="n"/>
       <c r="C17" s="10" t="n"/>
       <c r="D17" s="10" t="n"/>
       <c r="E17" s="10" t="n"/>
@@ -1293,36 +1243,29 @@
       <c r="G17" s="11" t="n"/>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>15:30 - 17:00
+          <t>15:30-17:00
 Français
 Nassima</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="83" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="18" ht="63" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>9éme (B)</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
-        </is>
-      </c>
+      <c r="B18" s="16" t="n"/>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Arabe
 Yahya</t>
         </is>
@@ -1331,22 +1274,22 @@
       <c r="F18" s="10" t="n"/>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>17:30 - 19:00
+          <t>17:30-19:00
 Math
 Hajer</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>09:00 - 10:30
+          <t>09:00-10:30
 Anglais
 Bassma</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="67.8" customHeight="1">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="10" t="n"/>
+    <row r="19" ht="63" customHeight="1">
+      <c r="A19" s="17" t="n"/>
+      <c r="B19" s="16" t="n"/>
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="10" t="n"/>
       <c r="E19" s="10" t="n"/>
@@ -1354,95 +1297,80 @@
       <c r="G19" s="11" t="n"/>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 18:30
-Français
-Nassima
-⊕ 9éme (B) + 9éme (C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="83" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+          <t>17:00-18:30
+Français
+Nassima</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="63" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>9éme (C)</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
-        </is>
-      </c>
+      <c r="B20" s="12" t="n"/>
       <c r="C20" s="10" t="n"/>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Anglais
 Saber</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Arabe
 Yahya</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Math
 Hajer</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>17:00 - 18:30
-Français
-Nassima
-⊕ 9éme (B) + 9éme (C)</t>
-        </is>
-      </c>
+      <c r="H20" s="12" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>CYCLE SECONDAIRE   (8 classes)</t>
         </is>
       </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="17" t="n"/>
-      <c r="G21" s="17" t="n"/>
-      <c r="H21" s="17" t="n"/>
-    </row>
-    <row r="22" ht="52.59999999999999" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="19" t="n"/>
+    </row>
+    <row r="22" ht="63" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>1ére (A)</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Français
 Nassima</t>
         </is>
@@ -1451,7 +1379,7 @@
       <c r="E22" s="10" t="n"/>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>17:30 - 19:00
+          <t>17:30-19:00
 Arabe
 Najet</t>
         </is>
@@ -1459,14 +1387,14 @@
       <c r="G22" s="11" t="n"/>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>09:00 - 10:30
+          <t>09:00-10:30
 Physique
 Refka</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="52.59999999999999" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
+    <row r="23" ht="63" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>1ére (B)</t>
         </is>
@@ -1474,28 +1402,28 @@
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Français
 Nassima</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-B
+          <t>19:15-20:45 Q-B
 Anglais
 Imen Bennour</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Arabe
 Najet</t>
         </is>
@@ -1503,14 +1431,14 @@
       <c r="G23" s="11" t="n"/>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Physique
 Refka</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="52.59999999999999" customHeight="1">
-      <c r="A24" s="19" t="n"/>
+    <row r="24" ht="63" customHeight="1">
+      <c r="A24" s="17" t="n"/>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
@@ -1519,14 +1447,14 @@
       <c r="G24" s="11" t="n"/>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>13:00 - 14:30   ◆ Q-B
+          <t>13:00-14:30 Q-B
 SVT
 Imen Ghoumeme</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="83" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
+    <row r="25" ht="63" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>2éme Eco</t>
         </is>
@@ -1534,22 +1462,21 @@
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00   ◆ Q-B
+          <t>19:30-21:00 Q-B
 Arabe
-Najet
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
+Najet</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Gestion
 Yassine</t>
         </is>
@@ -1557,38 +1484,31 @@
       <c r="F25" s="10" t="n"/>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>15:30 - 17:00   ◆ Q-B
+          <t>15:30-17:00 Q-B
 Géographie
 Abdelwaheb</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>09:00 - 10:30
+          <t>09:00-10:30
 Eco
 Rym</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="83" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
+    <row r="26" ht="63" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>2éme SCE</t>
         </is>
       </c>
       <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00   ◆ Q-B
-Arabe
-Najet
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
-        </is>
-      </c>
+      <c r="C26" s="16" t="n"/>
       <c r="D26" s="10" t="n"/>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
@@ -1596,60 +1516,53 @@
       <c r="F26" s="10" t="n"/>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>16:00 - 17:30
+          <t>16:00-17:30
 SVT
 Rym</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>12:00 - 13:30
+          <t>12:00-13:30
 Physique
 Refka</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="83" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
+    <row r="27" ht="63" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>2éme INFO</t>
         </is>
       </c>
       <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00   ◆ Q-B
-Arabe
-Najet
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
-        </is>
-      </c>
+      <c r="C27" s="12" t="n"/>
       <c r="D27" s="10" t="n"/>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 19:00
+          <t>17:00-19:00
 Informatique
 Aymen</t>
         </is>
       </c>
       <c r="H27" s="11" t="n"/>
     </row>
-    <row r="28" ht="98.19999999999999" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
+    <row r="28" ht="63" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>3éme Eco</t>
         </is>
@@ -1657,218 +1570,172 @@
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-B   ◆ OPTION
+          <t>19:15-20:45 Q-B OPT
 Espagnol
-Imen
-⊕ 3éme Eco + 3éme INFO</t>
+Imen</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Gestion
 Yassine</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30   ◆ Q-B
+          <t>19:00-20:30 Q-B
 Philo
-Fayssel
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+Fayssel</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>17:30 - 19:00   ◆ Q-B
+          <t>17:30-19:00 Q-B
 Anglais
-Khaled
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+Khaled</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 18:30   ◆ Q-B
+          <t>17:00-18:30 Q-B
 Géographie
 Abdelwaheb</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Eco
 Rym</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="52.59999999999999" customHeight="1">
-      <c r="A29" s="19" t="n"/>
+    <row r="29" ht="63" customHeight="1">
+      <c r="A29" s="17" t="n"/>
       <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
+      <c r="C29" s="16" t="n"/>
       <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="16" t="n"/>
       <c r="G29" s="11" t="n"/>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>14:00 - 15:30
+          <t>14:00-15:30
 Math
 Lotfi</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="98.19999999999999" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+    <row r="30" ht="63" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>3éme INFO</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>15:30 - 17:30
+          <t>15:30-17:30
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45   ◆ Q-B   ◆ OPTION
-Espagnol
-Imen
-⊕ 3éme Eco + 3éme INFO</t>
-        </is>
-      </c>
+      <c r="C30" s="12" t="n"/>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>19:00 - 20:30   ◆ Q-B
-Philo
-Fayssel
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-B
-Anglais
-Khaled
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
-        </is>
-      </c>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>15:00 - 17:00
+          <t>15:00-17:00
 ALGO
 Aymen</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>12:00 - 13:30
+          <t>12:00-13:30
 Math
 Lotfi</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="98.19999999999999" customHeight="1">
-      <c r="A31" s="19" t="n"/>
+    <row r="31" ht="63" customHeight="1">
+      <c r="A31" s="17" t="n"/>
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-B   ◆ OPTION
+          <t>19:15-20:45 Q-B OPT
 Italien
-Amel
-⊕ 3éme INFO + 3éme SCE</t>
+Amel</t>
         </is>
       </c>
       <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
       <c r="G31" s="11" t="n"/>
       <c r="H31" s="11" t="n"/>
     </row>
-    <row r="32" ht="98.19999999999999" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="32" ht="63" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>3éme SCE</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Math
 Lotfi</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45   ◆ Q-B   ◆ OPTION
-Italien
-Amel
-⊕ 3éme INFO + 3éme SCE</t>
-        </is>
-      </c>
+      <c r="C32" s="12" t="n"/>
       <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>19:00 - 20:30   ◆ Q-B
-Philo
-Fayssel
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-B
-Anglais
-Khaled
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
-        </is>
-      </c>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>17:30 - 19:00
+          <t>17:30-19:00
 SVT
 Rym</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Physique
 Sondes</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>CYCLE BAC   (3 classes)</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n"/>
-      <c r="C33" s="21" t="n"/>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="21" t="n"/>
-      <c r="F33" s="21" t="n"/>
-      <c r="G33" s="21" t="n"/>
-      <c r="H33" s="21" t="n"/>
-    </row>
-    <row r="34" ht="83" customHeight="1">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="22" t="n"/>
+      <c r="H33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="63" customHeight="1">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>Bac Eco</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 Gestion
 Yassine</t>
         </is>
@@ -1877,60 +1744,58 @@
       <c r="D34" s="10" t="n"/>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00   ◆ Q-B
+          <t>19:30-21:00 Q-B
 Arabe
-Najet
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
+Najet</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>17:30 - 19:00   ◆ Q-B
-Français
-Nabil
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
+          <t>17:30-19:00 Q-B
+Français
+Nabil</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>18:30 - 20:00   ◆ Q-B
+          <t>18:30-20:00 Q-B
 Géographie
 Abdelwaheb</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Math
 Lotfi</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="52.59999999999999" customHeight="1">
-      <c r="A35" s="23" t="n"/>
+    <row r="35" ht="63" customHeight="1">
+      <c r="A35" s="17" t="n"/>
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="16" t="n"/>
       <c r="G35" s="11" t="n"/>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>12:30 - 14:30
+          <t>12:30-14:30
 Eco
 Rym</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="83" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
+    <row r="36" ht="63" customHeight="1">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>Bac SCE</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 Physique
 Sondes</t>
         </is>
@@ -1938,45 +1803,31 @@
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 Math
 Ahmed</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00   ◆ Q-B
-Arabe
-Najet
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-B
-Français
-Nabil
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
-        </is>
-      </c>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 SVT
 Rym</t>
         </is>
       </c>
       <c r="H36" s="11" t="n"/>
     </row>
-    <row r="37" ht="83" customHeight="1">
-      <c r="A37" s="22" t="inlineStr">
+    <row r="37" ht="63" customHeight="1">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>Bac INFO</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Physique
 Samia</t>
         </is>
@@ -1984,89 +1835,83 @@
       <c r="C37" s="10" t="n"/>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00   ◆ Q-B
-Arabe
-Najet
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-B
-Français
-Nabil
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
-        </is>
-      </c>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 ALGO
 Heni</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>15:30 - 17:00
+          <t>15:30-17:00
 Math
 Lotfi</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="26">
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="D11:D12"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="F28:F32"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="B16:B20"/>
     <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A28:A29"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A10:H10"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="E28:E32"/>
+    <mergeCell ref="C14:C15"/>
     <mergeCell ref="A30:A31"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:H37">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Arabe"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"عربية"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Français"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Anglais"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Espagnol"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Italien"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Math"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"رياضيات"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
+    <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Physique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"فيزياء"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"SVT"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Éveil scientifique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"إيقاظ علمي"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="5">
+    <cfRule type="expression" priority="6" dxfId="5" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Histoire"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Géographie"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Philo"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="6">
+    <cfRule type="expression" priority="7" dxfId="6" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Eco"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Gestion"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="7">
+    <cfRule type="expression" priority="8" dxfId="7" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Informatique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"ALGO"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"STI"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" dxfId="8">
-      <formula>ISNUMBER(SEARCH("◆ PONCTUEL",B5))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="10" dxfId="9">
-      <formula>ISNUMBER(SEARCH("◆ Q-",B5))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="11" dxfId="10" stopIfTrue="1">
+    <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
       <formula>LEN(B5)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2096,17 +1941,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2126,7 +1971,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Une case = une séance : horaire / matière / enseignant.   Couleur = famille de matières.   ◆ Q-A ou Q-B = une semaine sur deux.   ⊕ = séance partagée.   ◆ OPTION = cours au choix.</t>
+          <t>Une case = une séance : horaire / matière / enseignant.   Couleur = famille de matières.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2186,53 +2031,6 @@
         </is>
       </c>
     </row>
-    <row r="4" hidden="1" ht="3" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>__jour</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lundi</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Mardi</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Mercredi</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Jeudi</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Vendredi</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Samedi</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Dimanche</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-    </row>
     <row r="5" ht="21" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
@@ -2247,7 +2045,7 @@
       <c r="G5" s="8" t="n"/>
       <c r="H5" s="8" t="n"/>
     </row>
-    <row r="6" ht="52.59999999999999" customHeight="1">
+    <row r="6" ht="63" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>4éme</t>
@@ -2255,7 +2053,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 عربية
 Lobna</t>
         </is>
@@ -2263,7 +2061,7 @@
       <c r="C6" s="10" t="n"/>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 رياضيات
 Bassma</t>
         </is>
@@ -2271,27 +2069,27 @@
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30   ◆ Q-A
+          <t>19:00-20:30 Q-A
 إيقاظ علمي
 Bassma</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>16:00 - 17:30
+          <t>16:00-17:30
 Français
 Hend</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00   ◆ Q-A
+          <t>10:30-12:00 Q-A
 Anglais
 Samar</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="83" customHeight="1">
+    <row r="7" ht="99" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>5éme</t>
@@ -2300,7 +2098,7 @@
       <c r="B7" s="10" t="n"/>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 عربية
 Lobna</t>
         </is>
@@ -2308,7 +2106,7 @@
       <c r="D7" s="10" t="n"/>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 رياضيات
 Bassma
 Jour férié (Évacuation) — à confirmer</t>
@@ -2317,14 +2115,14 @@
       <c r="F7" s="10" t="n"/>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>18:00 - 19:30
+          <t>18:00-19:30
 Français
 Hend</t>
         </is>
       </c>
       <c r="H7" s="11" t="n"/>
     </row>
-    <row r="8" ht="83" customHeight="1">
+    <row r="8" ht="63" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>6éme Pilote (A)</t>
@@ -2332,7 +2130,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Français
 Hend</t>
         </is>
@@ -2340,7 +2138,7 @@
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 رياضيات
 Noura</t>
         </is>
@@ -2348,29 +2146,27 @@
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 إيقاظ علمي
-Noura
-⊕ 6éme Pilote (A) + 6éme (B)</t>
+Noura</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 عربية
 Lobna</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>12:00 - 13:30   ◆ Q-A
+          <t>12:00-13:30 Q-A
 Anglais
-Samar
-⊕ 6éme Pilote (A) + 6éme (B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="83" customHeight="1">
+Samar</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="99" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>6éme (B)</t>
@@ -2379,7 +2175,7 @@
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Français
 Hend</t>
         </is>
@@ -2387,52 +2183,38 @@
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 رياضيات
 Noura
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-إيقاظ علمي
-Noura
-⊕ 6éme Pilote (A) + 6éme (B)</t>
-        </is>
-      </c>
+      <c r="F9" s="12" t="n"/>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 19:00
+          <t>17:00-19:00
 عربية
 Lobna</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>12:00 - 13:30   ◆ Q-A
-Anglais
-Samar
-⊕ 6éme Pilote (A) + 6éme (B)</t>
-        </is>
-      </c>
+      <c r="H9" s="12" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>CYCLE COLLÈGE   (8 classes)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="67.8" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="63" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>7éme (A)</t>
         </is>
@@ -2440,84 +2222,76 @@
       <c r="B11" s="10" t="n"/>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30   ◆ Q-A
+          <t>19:00-20:30 Q-A
 Anglais
 Imen Ben Lazrak</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 فيزياء
-Melek
-⊕ 7éme (A) + 7éme (B)</t>
+Melek</t>
         </is>
       </c>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>18:00 - 19:30
+          <t>18:00-19:30
 Math
 Khouloud</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>16:00 - 17:30   ◆ Q-A
+          <t>16:00-17:30 Q-A
 SVT
 Sabrine</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>14:00 - 15:30
+          <t>14:00-15:30
 Français
 Marwa</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="52.59999999999999" customHeight="1">
-      <c r="A12" s="15" t="n"/>
+    <row r="12" ht="63" customHeight="1">
+      <c r="A12" s="17" t="n"/>
       <c r="B12" s="10" t="n"/>
       <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
+      <c r="D12" s="16" t="n"/>
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="n"/>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>18:00 - 19:30
+          <t>18:00-19:30
 Arabe
 Awatef</t>
         </is>
       </c>
       <c r="H12" s="11" t="n"/>
     </row>
-    <row r="13" ht="67.8" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+    <row r="13" ht="63" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>7éme (B)</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Arabe
 Yahya</t>
         </is>
       </c>
       <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 7éme (A) + 7éme (B)</t>
-        </is>
-      </c>
+      <c r="D13" s="12" t="n"/>
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Khouloud</t>
         </is>
@@ -2525,14 +2299,14 @@
       <c r="G13" s="11" t="n"/>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>15:30 - 17:00
+          <t>15:30-17:00
 Français
 Marwa</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="83" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+    <row r="14" ht="99" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>8éme (A)</t>
         </is>
@@ -2541,14 +2315,14 @@
       <c r="C14" s="10" t="n"/>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Arabe
 Awatef</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Français
 Nassima
 Jour férié (Évacuation) — à confirmer</t>
@@ -2556,29 +2330,28 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 فيزياء
-Melek
-⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
+Melek</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>17:30 - 19:00   ◆ Q-A
+          <t>17:30-19:00 Q-A
 SVT
 Sabrine</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>13:45 - 15:15
+          <t>13:45-15:15
 Math
 Hajer</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="83" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+    <row r="15" ht="63" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>8éme (B)</t>
         </is>
@@ -2586,109 +2359,78 @@
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Arabe
-Yahya
-⊕ 8éme (B) + 8éme (C)</t>
+Yahya</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Math
 Khouloud</t>
         </is>
       </c>
       <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
+      <c r="F15" s="16" t="n"/>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>17:30 - 19:00   ◆ Q-A
+          <t>17:30-19:00 Q-A
 Anglais
-Imen Ben Lazrak
-⊕ 8éme (B) + 8éme (C)</t>
+Imen Ben Lazrak</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 18:30
+          <t>17:00-18:30
 Français
 Marwa</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="83" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
+    <row r="16" ht="99" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>8éme (C)</t>
         </is>
       </c>
       <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-Arabe
-Yahya
-⊕ 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
+      <c r="C16" s="12" t="n"/>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Français
 Nabil</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Math
 Khouloud
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="11" t="n"/>
+    </row>
+    <row r="17" ht="99" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>9éme (A)</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>19:30-21:00
 فيزياء
-Melek
-⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-A
-Anglais
-Imen Ben Lazrak
-⊕ 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="n"/>
-    </row>
-    <row r="17" ht="83" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>9éme (A)</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
+Melek</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Math
 Faouzi</t>
         </is>
@@ -2696,7 +2438,7 @@
       <c r="D17" s="10" t="n"/>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 SVT
 Imen Jribi
 Jour férié (Évacuation) — à confirmer</t>
@@ -2705,22 +2447,22 @@
       <c r="F17" s="10" t="n"/>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>16:30 - 18:00
+          <t>16:30-18:00
 Arabe
 Awatef</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Anglais
 Bassma</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="52.59999999999999" customHeight="1">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="10" t="n"/>
+    <row r="18" ht="63" customHeight="1">
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="16" t="n"/>
       <c r="C18" s="10" t="n"/>
       <c r="D18" s="10" t="n"/>
       <c r="E18" s="10" t="n"/>
@@ -2728,36 +2470,29 @@
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>15:30 - 17:00
+          <t>15:30-17:00
 Français
 Nassima</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="83" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="19" ht="63" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>9éme (B)</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
-        </is>
-      </c>
+      <c r="B19" s="16" t="n"/>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Arabe
 Yahya</t>
         </is>
@@ -2766,22 +2501,22 @@
       <c r="F19" s="10" t="n"/>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>17:30 - 19:00
+          <t>17:30-19:00
 Math
 Hajer</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>09:00 - 10:30
+          <t>09:00-10:30
 Anglais
 Bassma</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="67.8" customHeight="1">
-      <c r="A20" s="15" t="n"/>
-      <c r="B20" s="10" t="n"/>
+    <row r="20" ht="63" customHeight="1">
+      <c r="A20" s="17" t="n"/>
+      <c r="B20" s="16" t="n"/>
       <c r="C20" s="10" t="n"/>
       <c r="D20" s="10" t="n"/>
       <c r="E20" s="10" t="n"/>
@@ -2789,38 +2524,30 @@
       <c r="G20" s="11" t="n"/>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 18:30
-Français
-Nassima
-⊕ 9éme (B) + 9éme (C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="83" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
+          <t>17:00-18:30
+Français
+Nassima</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="99" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>9éme (C)</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
-        </is>
-      </c>
+      <c r="B21" s="12" t="n"/>
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Anglais
 Saber
 Jour férié (Évacuation) — à confirmer</t>
@@ -2828,57 +2555,50 @@
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Arabe
 Yahya</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Math
 Hajer</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>17:00 - 18:30
-Français
-Nassima
-⊕ 9éme (B) + 9éme (C)</t>
-        </is>
-      </c>
+      <c r="H21" s="12" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>CYCLE SECONDAIRE   (8 classes)</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="17" t="n"/>
-      <c r="G22" s="17" t="n"/>
-      <c r="H22" s="17" t="n"/>
-    </row>
-    <row r="23" ht="83" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="19" t="n"/>
+    </row>
+    <row r="23" ht="99" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>1ére (A)</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Français
 Nassima</t>
         </is>
@@ -2886,7 +2606,7 @@
       <c r="D23" s="10" t="n"/>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-A
+          <t>19:15-20:45 Q-A
 Anglais
 Imen Bennour
 Jour férié (Évacuation) — à confirmer</t>
@@ -2894,7 +2614,7 @@
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>17:30 - 19:00
+          <t>17:30-19:00
 Arabe
 Najet</t>
         </is>
@@ -2902,14 +2622,14 @@
       <c r="G23" s="11" t="n"/>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>09:00 - 10:30
+          <t>09:00-10:30
 Physique
 Refka</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="52.59999999999999" customHeight="1">
-      <c r="A24" s="19" t="n"/>
+    <row r="24" ht="63" customHeight="1">
+      <c r="A24" s="17" t="n"/>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
@@ -2918,14 +2638,14 @@
       <c r="G24" s="11" t="n"/>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>13:00 - 14:30   ◆ Q-A
+          <t>13:00-14:30 Q-A
 SVT
 Imen Ghoumeme</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="52.59999999999999" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
+    <row r="25" ht="63" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>1ére (B)</t>
         </is>
@@ -2933,14 +2653,14 @@
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Français
 Nassima</t>
         </is>
@@ -2948,7 +2668,7 @@
       <c r="E25" s="10" t="n"/>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Arabe
 Najet</t>
         </is>
@@ -2956,14 +2676,14 @@
       <c r="G25" s="11" t="n"/>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Physique
 Refka</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="83" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
+    <row r="26" ht="99" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>2éme Eco</t>
         </is>
@@ -2971,22 +2691,21 @@
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-A
+          <t>19:15-20:45 Q-A
 Anglais
-Imen Bennour
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
+Imen Bennour</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Gestion
 Yassine
 Jour férié (Évacuation) — à confirmer</t>
@@ -2994,124 +2713,95 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>17:30 - 19:00   ◆ Q-A
-Français
-Nabil
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
+          <t>17:30-19:00 Q-A
+Français
+Nabil</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>15:30 - 17:00   ◆ Q-A
+          <t>15:30-17:00 Q-A
 Histoire
 Abdelwaheb</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>09:00 - 10:30
+          <t>09:00-10:30
 Eco
 Rym</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="83" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
+    <row r="27" ht="99" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>2éme SCE</t>
         </is>
       </c>
       <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45   ◆ Q-A
-Anglais
-Imen Bennour
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
-        </is>
-      </c>
+      <c r="C27" s="16" t="n"/>
       <c r="D27" s="10" t="n"/>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-A
-Français
-Nabil
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
-        </is>
-      </c>
+      <c r="F27" s="16" t="n"/>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>16:00 - 17:30
+          <t>16:00-17:30
 SVT
 Rym</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>12:00 - 13:30
+          <t>12:00-13:30
 Physique
 Refka</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="83" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
+    <row r="28" ht="99" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>2éme INFO</t>
         </is>
       </c>
       <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45   ◆ Q-A
-Anglais
-Imen Bennour
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
-        </is>
-      </c>
+      <c r="C28" s="16" t="n"/>
       <c r="D28" s="10" t="n"/>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Physique
 Samia
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-A
-Français
-Nabil
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
-        </is>
-      </c>
+      <c r="F28" s="12" t="n"/>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 19:00
+          <t>17:00-19:00
 Informatique
 Aymen</t>
         </is>
       </c>
       <c r="H28" s="11" t="n"/>
     </row>
-    <row r="29" ht="52.59999999999999" customHeight="1">
-      <c r="A29" s="19" t="n"/>
+    <row r="29" ht="63" customHeight="1">
+      <c r="A29" s="17" t="n"/>
       <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
+      <c r="C29" s="12" t="n"/>
       <c r="D29" s="10" t="n"/>
       <c r="E29" s="10" t="n"/>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
@@ -3119,8 +2809,8 @@
       <c r="G29" s="11" t="n"/>
       <c r="H29" s="11" t="n"/>
     </row>
-    <row r="30" ht="113.4" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+    <row r="30" ht="63" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>3éme Eco</t>
         </is>
@@ -3129,68 +2819,66 @@
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Gestion
 Yassine</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00   ◆ Q-A
+          <t>19:30-21:00 Q-A
 Arabe
 Najet
-⊕ 3éme Eco + 3éme INFO + 3éme SCE
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30   ◆ Q-A
-Français
-Nabil
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+          <t>19:00-20:30 Q-A
+Français
+Nabil</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 18:30   ◆ Q-A
+          <t>17:00-18:30 Q-A
 Histoire
 Abdelwaheb</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Eco
 Rym</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="52.59999999999999" customHeight="1">
-      <c r="A31" s="19" t="n"/>
+    <row r="31" ht="63" customHeight="1">
+      <c r="A31" s="17" t="n"/>
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="10" t="n"/>
       <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
       <c r="G31" s="11" t="n"/>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>14:00 - 15:30
+          <t>14:00-15:30
 Math
 Lotfi</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="113.4" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="32" ht="63" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>3éme INFO</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>15:30 - 17:30
+          <t>15:30-17:30
 STI
 Aymen</t>
         </is>
@@ -3198,354 +2886,286 @@
       <c r="C32" s="10" t="n"/>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00   ◆ Q-A
-Arabe
-Najet
-⊕ 3éme Eco + 3éme INFO + 3éme SCE
-Jour férié (Évacuation) — à confirmer</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>19:00 - 20:30   ◆ Q-A
-Français
-Nabil
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
-        </is>
-      </c>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>15:00 - 17:00
+          <t>15:00-17:00
 ALGO
 Aymen</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>12:00 - 13:30
+          <t>12:00-13:30
 Math
 Lotfi</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="113.4" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="33" ht="63" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>3éme SCE</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Math
 Lotfi</t>
         </is>
       </c>
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00   ◆ Q-A
-Arabe
-Najet
-⊕ 3éme Eco + 3éme INFO + 3éme SCE
-Jour férié (Évacuation) — à confirmer</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>19:00 - 20:30   ◆ Q-A
-Français
-Nabil
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
-        </is>
-      </c>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>17:30 - 19:00
+          <t>17:30-19:00
 SVT
 Rym</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Physique
 Sondes</t>
         </is>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>CYCLE BAC   (3 classes)</t>
         </is>
       </c>
-      <c r="B34" s="21" t="n"/>
-      <c r="C34" s="21" t="n"/>
-      <c r="D34" s="21" t="n"/>
-      <c r="E34" s="21" t="n"/>
-      <c r="F34" s="21" t="n"/>
-      <c r="G34" s="21" t="n"/>
-      <c r="H34" s="21" t="n"/>
-    </row>
-    <row r="35" ht="113.4" customHeight="1">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="22" t="n"/>
+      <c r="H34" s="22" t="n"/>
+    </row>
+    <row r="35" ht="63" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>Bac Eco</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 Gestion
 Yassine</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-A   ◆ OPTION
+          <t>19:15-20:45 Q-A OPT
 Espagnol
-Imen
-⊕ Bac Eco + Bac SCE</t>
+Imen</t>
         </is>
       </c>
       <c r="D35" s="10" t="n"/>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30   ◆ Q-A
+          <t>19:00-20:30 Q-A
 Philo
 Fayssel
-⊕ Bac Eco + Bac SCE + Bac INFO
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>17:30 - 19:00   ◆ Q-A
+          <t>17:30-19:00 Q-A
 Anglais
-Khaled
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
+Khaled</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>18:30 - 20:00   ◆ Q-A
+          <t>18:30-20:00 Q-A
 Histoire
 Abdelwaheb</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Math
 Lotfi</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="52.59999999999999" customHeight="1">
-      <c r="A36" s="23" t="n"/>
+    <row r="36" ht="63" customHeight="1">
+      <c r="A36" s="17" t="n"/>
       <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
+      <c r="C36" s="16" t="n"/>
       <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
       <c r="G36" s="11" t="n"/>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>12:30 - 14:30
+          <t>12:30-14:30
 Eco
 Rym</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="113.4" customHeight="1">
-      <c r="A37" s="22" t="inlineStr">
+    <row r="37" ht="63" customHeight="1">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>Bac SCE</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 Physique
 Sondes</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45   ◆ Q-A   ◆ OPTION
-Espagnol
-Imen
-⊕ Bac Eco + Bac SCE</t>
-        </is>
-      </c>
+      <c r="C37" s="12" t="n"/>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 Math
 Ahmed</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>19:00 - 20:30   ◆ Q-A
-Philo
-Fayssel
-⊕ Bac Eco + Bac SCE + Bac INFO
-Jour férié (Évacuation) — à confirmer</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-A
-Anglais
-Khaled
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
-        </is>
-      </c>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 SVT
 Rym</t>
         </is>
       </c>
       <c r="H37" s="11" t="n"/>
     </row>
-    <row r="38" ht="83" customHeight="1">
-      <c r="A38" s="23" t="n"/>
+    <row r="38" ht="63" customHeight="1">
+      <c r="A38" s="17" t="n"/>
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-A   ◆ OPTION
+          <t>19:15-20:45 Q-A OPT
 Italien
-Amel
-⊕ Bac SCE + Bac INFO</t>
+Amel</t>
         </is>
       </c>
       <c r="D38" s="10" t="n"/>
-      <c r="E38" s="10" t="n"/>
-      <c r="F38" s="10" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
       <c r="G38" s="11" t="n"/>
       <c r="H38" s="11" t="n"/>
     </row>
-    <row r="39" ht="113.4" customHeight="1">
-      <c r="A39" s="22" t="inlineStr">
+    <row r="39" ht="63" customHeight="1">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>Bac INFO</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45   ◆ Q-A   ◆ OPTION
-Italien
-Amel
-⊕ Bac SCE + Bac INFO</t>
-        </is>
-      </c>
+      <c r="C39" s="12" t="n"/>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>19:00 - 20:30   ◆ Q-A
-Philo
-Fayssel
-⊕ Bac Eco + Bac SCE + Bac INFO
-Jour férié (Évacuation) — à confirmer</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-A
-Anglais
-Khaled
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
-        </is>
-      </c>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="12" t="n"/>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 ALGO
 Heni</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>15:30 - 17:00
+          <t>15:30-17:00
 Math
 Lotfi</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="30">
+    <mergeCell ref="F35:F39"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="F30:F33"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="E30:E33"/>
     <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A28:A29"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A10:H10"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="E35:E39"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="C15:C16"/>
     <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A34:H34"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:H39">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Arabe"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"عربية"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Français"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Anglais"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Espagnol"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Italien"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Math"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"رياضيات"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
+    <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Physique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"فيزياء"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"SVT"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Éveil scientifique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"إيقاظ علمي"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="5">
+    <cfRule type="expression" priority="6" dxfId="5" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Histoire"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Géographie"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Philo"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="6">
+    <cfRule type="expression" priority="7" dxfId="6" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Eco"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Gestion"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="7">
+    <cfRule type="expression" priority="8" dxfId="7" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Informatique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"ALGO"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"STI"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" dxfId="8">
-      <formula>ISNUMBER(SEARCH("◆ PONCTUEL",B5))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="10" dxfId="9">
-      <formula>ISNUMBER(SEARCH("◆ Q-",B5))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="11" dxfId="10" stopIfTrue="1">
+    <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
       <formula>LEN(B5)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3575,17 +3195,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3605,7 +3225,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Une case = une séance : horaire / matière / enseignant.   Couleur = famille de matières.   ◆ Q-A ou Q-B = une semaine sur deux.   ⊕ = séance partagée.   ◆ OPTION = cours au choix.</t>
+          <t>Une case = une séance : horaire / matière / enseignant.   Couleur = famille de matières.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3665,53 +3285,6 @@
         </is>
       </c>
     </row>
-    <row r="4" hidden="1" ht="3" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>__jour</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lundi</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Mardi</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Mercredi</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Jeudi</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Vendredi</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Samedi</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Dimanche</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-    </row>
     <row r="5" ht="21" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
@@ -3726,7 +3299,7 @@
       <c r="G5" s="8" t="n"/>
       <c r="H5" s="8" t="n"/>
     </row>
-    <row r="6" ht="52.59999999999999" customHeight="1">
+    <row r="6" ht="63" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>4éme</t>
@@ -3734,7 +3307,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 عربية
 Lobna</t>
         </is>
@@ -3742,7 +3315,7 @@
       <c r="C6" s="10" t="n"/>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 رياضيات
 Bassma</t>
         </is>
@@ -3751,14 +3324,14 @@
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>16:00 - 17:30
+          <t>16:00-17:30
 Français
 Hend</t>
         </is>
       </c>
       <c r="H6" s="11" t="n"/>
     </row>
-    <row r="7" ht="52.59999999999999" customHeight="1">
+    <row r="7" ht="63" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>5éme</t>
@@ -3767,7 +3340,7 @@
       <c r="B7" s="10" t="n"/>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 عربية
 Lobna</t>
         </is>
@@ -3775,34 +3348,34 @@
       <c r="D7" s="10" t="n"/>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 رياضيات
 Bassma</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30   ◆ Q-B
+          <t>19:00-20:30 Q-B
 إيقاظ علمي
 Bassma</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>18:00 - 19:30
+          <t>18:00-19:30
 Français
 Hend</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00   ◆ Q-B
+          <t>10:30-12:00 Q-B
 Anglais
 Samar</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="83" customHeight="1">
+    <row r="8" ht="63" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>6éme Pilote (A)</t>
@@ -3810,7 +3383,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Français
 Hend</t>
         </is>
@@ -3818,7 +3391,7 @@
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 رياضيات
 Noura</t>
         </is>
@@ -3826,22 +3399,21 @@
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 إيقاظ علمي
-Noura
-⊕ 6éme Pilote (A) + 6éme (B)</t>
+Noura</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 عربية
 Lobna</t>
         </is>
       </c>
       <c r="H8" s="11" t="n"/>
     </row>
-    <row r="9" ht="83" customHeight="1">
+    <row r="9" ht="63" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>6éme (B)</t>
@@ -3850,7 +3422,7 @@
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Français
 Hend</t>
         </is>
@@ -3858,22 +3430,15 @@
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 رياضيات
 Noura</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-إيقاظ علمي
-Noura
-⊕ 6éme Pilote (A) + 6éme (B)</t>
-        </is>
-      </c>
+      <c r="F9" s="12" t="n"/>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 19:00
+          <t>17:00-19:00
 عربية
 Lobna</t>
         </is>
@@ -3881,21 +3446,21 @@
       <c r="H9" s="11" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>CYCLE COLLÈGE   (8 classes)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="67.8" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="63" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>7éme (A)</t>
         </is>
@@ -3904,88 +3469,80 @@
       <c r="C11" s="10" t="n"/>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 فيزياء
-Melek
-⊕ 7éme (A) + 7éme (B)</t>
+Melek</t>
         </is>
       </c>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>18:00 - 19:30
+          <t>18:00-19:30
 Math
 Khouloud</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>18:00 - 19:30
+          <t>18:00-19:30
 Arabe
 Awatef</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>14:00 - 15:30
+          <t>14:00-15:30
 Français
 Marwa</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="67.8" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="12" ht="63" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>7éme (B)</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Arabe
 Yahya</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30   ◆ Q-B
+          <t>19:00-20:30 Q-B
 Anglais
 Imen Ben Lazrak</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 7éme (A) + 7éme (B)</t>
-        </is>
-      </c>
+      <c r="D12" s="12" t="n"/>
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Khouloud</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>16:00 - 17:30   ◆ Q-B
+          <t>16:00-17:30 Q-B
 SVT
 Sabrine</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>15:30 - 17:00
+          <t>15:30-17:00
 Français
 Marwa</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="83" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+    <row r="13" ht="63" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>8éme (A)</t>
         </is>
@@ -3994,43 +3551,42 @@
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Arabe
 Awatef</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Français
 Nassima</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 فيزياء
-Melek
-⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
+Melek</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>17:30 - 19:00   ◆ Q-B
+          <t>17:30-19:00 Q-B
 Anglais
 Imen Ben Lazrak</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>13:45 - 15:15
+          <t>13:45-15:15
 Math
 Hajer</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="83" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+    <row r="14" ht="63" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>8éme (B)</t>
         </is>
@@ -4038,108 +3594,77 @@
       <c r="B14" s="10" t="n"/>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Arabe
-Yahya
-⊕ 8éme (B) + 8éme (C)</t>
+Yahya</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Math
 Khouloud</t>
         </is>
       </c>
       <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>17:30-19:00 Q-B
+SVT
+Sabrine</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>17:00-18:30
+Français
+Marwa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="63" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>8éme (C)</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>19:30-21:00
+Français
+Nabil</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>19:15-20:45
+Math
+Khouloud</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="11" t="n"/>
+    </row>
+    <row r="16" ht="63" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>9éme (A)</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>19:30-21:00
 فيزياء
-Melek
-⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-B
-SVT
-Sabrine
-⊕ 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>17:00 - 18:30
-Français
-Marwa</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="83" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>8éme (C)</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-Arabe
-Yahya
-⊕ 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-Français
-Nabil</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45
-Math
-Khouloud</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-B
-SVT
-Sabrine
-⊕ 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="n"/>
-    </row>
-    <row r="16" ht="83" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>9éme (A)</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
+Melek</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Math
 Faouzi</t>
         </is>
@@ -4147,7 +3672,7 @@
       <c r="D16" s="10" t="n"/>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
@@ -4155,22 +3680,22 @@
       <c r="F16" s="10" t="n"/>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>16:30 - 18:00
+          <t>16:30-18:00
 Arabe
 Awatef</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Anglais
 Bassma</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="52.59999999999999" customHeight="1">
-      <c r="A17" s="15" t="n"/>
-      <c r="B17" s="10" t="n"/>
+    <row r="17" ht="63" customHeight="1">
+      <c r="A17" s="17" t="n"/>
+      <c r="B17" s="16" t="n"/>
       <c r="C17" s="10" t="n"/>
       <c r="D17" s="10" t="n"/>
       <c r="E17" s="10" t="n"/>
@@ -4178,36 +3703,29 @@
       <c r="G17" s="11" t="n"/>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>15:30 - 17:00
+          <t>15:30-17:00
 Français
 Nassima</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="83" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="18" ht="63" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>9éme (B)</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
-        </is>
-      </c>
+      <c r="B18" s="16" t="n"/>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Arabe
 Yahya</t>
         </is>
@@ -4216,22 +3734,22 @@
       <c r="F18" s="10" t="n"/>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>17:30 - 19:00
+          <t>17:30-19:00
 Math
 Hajer</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>09:00 - 10:30
+          <t>09:00-10:30
 Anglais
 Bassma</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="67.8" customHeight="1">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="10" t="n"/>
+    <row r="19" ht="63" customHeight="1">
+      <c r="A19" s="17" t="n"/>
+      <c r="B19" s="16" t="n"/>
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="10" t="n"/>
       <c r="E19" s="10" t="n"/>
@@ -4239,95 +3757,80 @@
       <c r="G19" s="11" t="n"/>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 18:30
-Français
-Nassima
-⊕ 9éme (B) + 9éme (C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="83" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+          <t>17:00-18:30
+Français
+Nassima</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="63" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>9éme (C)</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
-        </is>
-      </c>
+      <c r="B20" s="12" t="n"/>
       <c r="C20" s="10" t="n"/>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Anglais
 Saber</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Arabe
 Yahya</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Math
 Hajer</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>17:00 - 18:30
-Français
-Nassima
-⊕ 9éme (B) + 9éme (C)</t>
-        </is>
-      </c>
+      <c r="H20" s="12" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>CYCLE SECONDAIRE   (8 classes)</t>
         </is>
       </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="17" t="n"/>
-      <c r="G21" s="17" t="n"/>
-      <c r="H21" s="17" t="n"/>
-    </row>
-    <row r="22" ht="52.59999999999999" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="19" t="n"/>
+    </row>
+    <row r="22" ht="63" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>1ére (A)</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Français
 Nassima</t>
         </is>
@@ -4336,7 +3839,7 @@
       <c r="E22" s="10" t="n"/>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>17:30 - 19:00
+          <t>17:30-19:00
 Arabe
 Najet</t>
         </is>
@@ -4344,14 +3847,14 @@
       <c r="G22" s="11" t="n"/>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>09:00 - 10:30
+          <t>09:00-10:30
 Physique
 Refka</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="52.59999999999999" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
+    <row r="23" ht="63" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>1ére (B)</t>
         </is>
@@ -4359,28 +3862,28 @@
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Français
 Nassima</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-B
+          <t>19:15-20:45 Q-B
 Anglais
 Imen Bennour</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Arabe
 Najet</t>
         </is>
@@ -4388,14 +3891,14 @@
       <c r="G23" s="11" t="n"/>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Physique
 Refka</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="52.59999999999999" customHeight="1">
-      <c r="A24" s="19" t="n"/>
+    <row r="24" ht="63" customHeight="1">
+      <c r="A24" s="17" t="n"/>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
@@ -4404,14 +3907,14 @@
       <c r="G24" s="11" t="n"/>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>13:00 - 14:30   ◆ Q-B
+          <t>13:00-14:30 Q-B
 SVT
 Imen Ghoumeme</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="83" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
+    <row r="25" ht="63" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>2éme Eco</t>
         </is>
@@ -4419,22 +3922,21 @@
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00   ◆ Q-B
+          <t>19:30-21:00 Q-B
 Arabe
-Najet
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
+Najet</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Gestion
 Yassine</t>
         </is>
@@ -4442,38 +3944,31 @@
       <c r="F25" s="10" t="n"/>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>15:30 - 17:00   ◆ Q-B
+          <t>15:30-17:00 Q-B
 Géographie
 Abdelwaheb</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>09:00 - 10:30
+          <t>09:00-10:30
 Eco
 Rym</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="83" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
+    <row r="26" ht="63" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>2éme SCE</t>
         </is>
       </c>
       <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00   ◆ Q-B
-Arabe
-Najet
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
-        </is>
-      </c>
+      <c r="C26" s="16" t="n"/>
       <c r="D26" s="10" t="n"/>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
@@ -4481,60 +3976,53 @@
       <c r="F26" s="10" t="n"/>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>16:00 - 17:30
+          <t>16:00-17:30
 SVT
 Rym</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>12:00 - 13:30
+          <t>12:00-13:30
 Physique
 Refka</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="83" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
+    <row r="27" ht="63" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>2éme INFO</t>
         </is>
       </c>
       <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00   ◆ Q-B
-Arabe
-Najet
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
-        </is>
-      </c>
+      <c r="C27" s="12" t="n"/>
       <c r="D27" s="10" t="n"/>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 19:00
+          <t>17:00-19:00
 Informatique
 Aymen</t>
         </is>
       </c>
       <c r="H27" s="11" t="n"/>
     </row>
-    <row r="28" ht="98.19999999999999" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
+    <row r="28" ht="63" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>3éme Eco</t>
         </is>
@@ -4542,218 +4030,172 @@
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-B   ◆ OPTION
+          <t>19:15-20:45 Q-B OPT
 Espagnol
-Imen
-⊕ 3éme Eco + 3éme INFO</t>
+Imen</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Gestion
 Yassine</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30   ◆ Q-B
+          <t>19:00-20:30 Q-B
 Philo
-Fayssel
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+Fayssel</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>17:30 - 19:00   ◆ Q-B
+          <t>17:30-19:00 Q-B
 Anglais
-Khaled
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+Khaled</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 18:30   ◆ Q-B
+          <t>17:00-18:30 Q-B
 Géographie
 Abdelwaheb</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Eco
 Rym</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="52.59999999999999" customHeight="1">
-      <c r="A29" s="19" t="n"/>
+    <row r="29" ht="63" customHeight="1">
+      <c r="A29" s="17" t="n"/>
       <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
+      <c r="C29" s="16" t="n"/>
       <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="16" t="n"/>
       <c r="G29" s="11" t="n"/>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>14:00 - 15:30
+          <t>14:00-15:30
 Math
 Lotfi</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="98.19999999999999" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+    <row r="30" ht="63" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>3éme INFO</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>15:30 - 17:30
+          <t>15:30-17:30
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45   ◆ Q-B   ◆ OPTION
-Espagnol
-Imen
-⊕ 3éme Eco + 3éme INFO</t>
-        </is>
-      </c>
+      <c r="C30" s="12" t="n"/>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>19:00 - 20:30   ◆ Q-B
-Philo
-Fayssel
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-B
-Anglais
-Khaled
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
-        </is>
-      </c>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>15:00 - 17:00
+          <t>15:00-17:00
 ALGO
 Aymen</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>12:00 - 13:30
+          <t>12:00-13:30
 Math
 Lotfi</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="98.19999999999999" customHeight="1">
-      <c r="A31" s="19" t="n"/>
+    <row r="31" ht="63" customHeight="1">
+      <c r="A31" s="17" t="n"/>
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-B   ◆ OPTION
+          <t>19:15-20:45 Q-B OPT
 Italien
-Amel
-⊕ 3éme INFO + 3éme SCE</t>
+Amel</t>
         </is>
       </c>
       <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
       <c r="G31" s="11" t="n"/>
       <c r="H31" s="11" t="n"/>
     </row>
-    <row r="32" ht="98.19999999999999" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="32" ht="63" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>3éme SCE</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Math
 Lotfi</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45   ◆ Q-B   ◆ OPTION
-Italien
-Amel
-⊕ 3éme INFO + 3éme SCE</t>
-        </is>
-      </c>
+      <c r="C32" s="12" t="n"/>
       <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>19:00 - 20:30   ◆ Q-B
-Philo
-Fayssel
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-B
-Anglais
-Khaled
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
-        </is>
-      </c>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>17:30 - 19:00
+          <t>17:30-19:00
 SVT
 Rym</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Physique
 Sondes</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>CYCLE BAC   (3 classes)</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n"/>
-      <c r="C33" s="21" t="n"/>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="21" t="n"/>
-      <c r="F33" s="21" t="n"/>
-      <c r="G33" s="21" t="n"/>
-      <c r="H33" s="21" t="n"/>
-    </row>
-    <row r="34" ht="83" customHeight="1">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="22" t="n"/>
+      <c r="H33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="63" customHeight="1">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>Bac Eco</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 Gestion
 Yassine</t>
         </is>
@@ -4762,60 +4204,58 @@
       <c r="D34" s="10" t="n"/>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00   ◆ Q-B
+          <t>19:30-21:00 Q-B
 Arabe
-Najet
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
+Najet</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>17:30 - 19:00   ◆ Q-B
-Français
-Nabil
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
+          <t>17:30-19:00 Q-B
+Français
+Nabil</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>18:30 - 20:00   ◆ Q-B
+          <t>18:30-20:00 Q-B
 Géographie
 Abdelwaheb</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Math
 Lotfi</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="52.59999999999999" customHeight="1">
-      <c r="A35" s="23" t="n"/>
+    <row r="35" ht="63" customHeight="1">
+      <c r="A35" s="17" t="n"/>
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="16" t="n"/>
       <c r="G35" s="11" t="n"/>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>12:30 - 14:30
+          <t>12:30-14:30
 Eco
 Rym</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="83" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
+    <row r="36" ht="63" customHeight="1">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>Bac SCE</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 Physique
 Sondes</t>
         </is>
@@ -4823,45 +4263,31 @@
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 Math
 Ahmed</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00   ◆ Q-B
-Arabe
-Najet
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-B
-Français
-Nabil
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
-        </is>
-      </c>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 SVT
 Rym</t>
         </is>
       </c>
       <c r="H36" s="11" t="n"/>
     </row>
-    <row r="37" ht="83" customHeight="1">
-      <c r="A37" s="22" t="inlineStr">
+    <row r="37" ht="63" customHeight="1">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>Bac INFO</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Physique
 Samia</t>
         </is>
@@ -4869,89 +4295,83 @@
       <c r="C37" s="10" t="n"/>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00   ◆ Q-B
-Arabe
-Najet
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-B
-Français
-Nabil
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
-        </is>
-      </c>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 ALGO
 Heni</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>15:30 - 17:00
+          <t>15:30-17:00
 Math
 Lotfi</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="26">
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="D11:D12"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="F28:F32"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="B16:B20"/>
     <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A28:A29"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A10:H10"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="E28:E32"/>
+    <mergeCell ref="C14:C15"/>
     <mergeCell ref="A30:A31"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:H37">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Arabe"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"عربية"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Français"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Anglais"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Espagnol"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Italien"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Math"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"رياضيات"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
+    <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Physique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"فيزياء"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"SVT"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Éveil scientifique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"إيقاظ علمي"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="5">
+    <cfRule type="expression" priority="6" dxfId="5" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Histoire"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Géographie"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Philo"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="6">
+    <cfRule type="expression" priority="7" dxfId="6" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Eco"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Gestion"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="7">
+    <cfRule type="expression" priority="8" dxfId="7" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Informatique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"ALGO"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"STI"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" dxfId="8">
-      <formula>ISNUMBER(SEARCH("◆ PONCTUEL",B5))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="10" dxfId="9">
-      <formula>ISNUMBER(SEARCH("◆ Q-",B5))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="11" dxfId="10" stopIfTrue="1">
+    <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
       <formula>LEN(B5)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4981,17 +4401,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -5011,7 +4431,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Une case = une séance : horaire / matière / enseignant.   Couleur = famille de matières.   ◆ Q-A ou Q-B = une semaine sur deux.   ⊕ = séance partagée.   ◆ OPTION = cours au choix.</t>
+          <t>Une case = une séance : horaire / matière / enseignant.   Couleur = famille de matières.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5071,53 +4491,6 @@
         </is>
       </c>
     </row>
-    <row r="4" hidden="1" ht="3" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>__jour</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lundi</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Mardi</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Mercredi</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Jeudi</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Vendredi</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Samedi</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Dimanche</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-    </row>
     <row r="5" ht="21" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
@@ -5132,7 +4505,7 @@
       <c r="G5" s="8" t="n"/>
       <c r="H5" s="8" t="n"/>
     </row>
-    <row r="6" ht="52.59999999999999" customHeight="1">
+    <row r="6" ht="63" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>4éme</t>
@@ -5140,7 +4513,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 عربية
 Lobna</t>
         </is>
@@ -5148,7 +4521,7 @@
       <c r="C6" s="10" t="n"/>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 رياضيات
 Bassma</t>
         </is>
@@ -5156,27 +4529,27 @@
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30   ◆ Q-A
+          <t>19:00-20:30 Q-A
 إيقاظ علمي
 Bassma</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>16:00 - 17:30
+          <t>16:00-17:30
 Français
 Hend</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00   ◆ Q-A
+          <t>10:30-12:00 Q-A
 Anglais
 Samar</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="52.59999999999999" customHeight="1">
+    <row r="7" ht="63" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>5éme</t>
@@ -5185,7 +4558,7 @@
       <c r="B7" s="10" t="n"/>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 عربية
 Lobna</t>
         </is>
@@ -5193,7 +4566,7 @@
       <c r="D7" s="10" t="n"/>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 رياضيات
 Bassma</t>
         </is>
@@ -5201,14 +4574,14 @@
       <c r="F7" s="10" t="n"/>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>18:00 - 19:30
+          <t>18:00-19:30
 Français
 Hend</t>
         </is>
       </c>
       <c r="H7" s="11" t="n"/>
     </row>
-    <row r="8" ht="83" customHeight="1">
+    <row r="8" ht="63" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>6éme Pilote (A)</t>
@@ -5216,7 +4589,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Français
 Hend</t>
         </is>
@@ -5224,7 +4597,7 @@
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 رياضيات
 Noura</t>
         </is>
@@ -5232,29 +4605,27 @@
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 إيقاظ علمي
-Noura
-⊕ 6éme Pilote (A) + 6éme (B)</t>
+Noura</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 عربية
 Lobna</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>12:00 - 13:30   ◆ Q-A
+          <t>12:00-13:30 Q-A
 Anglais
-Samar
-⊕ 6éme Pilote (A) + 6éme (B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="83" customHeight="1">
+Samar</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="63" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>6éme (B)</t>
@@ -5263,7 +4634,7 @@
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Français
 Hend</t>
         </is>
@@ -5271,51 +4642,37 @@
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 رياضيات
 Noura</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-إيقاظ علمي
-Noura
-⊕ 6éme Pilote (A) + 6éme (B)</t>
-        </is>
-      </c>
+      <c r="F9" s="12" t="n"/>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 19:00
+          <t>17:00-19:00
 عربية
 Lobna</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>12:00 - 13:30   ◆ Q-A
-Anglais
-Samar
-⊕ 6éme Pilote (A) + 6éme (B)</t>
-        </is>
-      </c>
+      <c r="H9" s="12" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>CYCLE COLLÈGE   (8 classes)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="67.8" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="63" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>7éme (A)</t>
         </is>
@@ -5323,84 +4680,76 @@
       <c r="B11" s="10" t="n"/>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30   ◆ Q-A
+          <t>19:00-20:30 Q-A
 Anglais
 Imen Ben Lazrak</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 فيزياء
-Melek
-⊕ 7éme (A) + 7éme (B)</t>
+Melek</t>
         </is>
       </c>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>18:00 - 19:30
+          <t>18:00-19:30
 Math
 Khouloud</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>16:00 - 17:30   ◆ Q-A
+          <t>16:00-17:30 Q-A
 SVT
 Sabrine</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>14:00 - 15:30
+          <t>14:00-15:30
 Français
 Marwa</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="52.59999999999999" customHeight="1">
-      <c r="A12" s="15" t="n"/>
+    <row r="12" ht="63" customHeight="1">
+      <c r="A12" s="17" t="n"/>
       <c r="B12" s="10" t="n"/>
       <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
+      <c r="D12" s="16" t="n"/>
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="n"/>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>18:00 - 19:30
+          <t>18:00-19:30
 Arabe
 Awatef</t>
         </is>
       </c>
       <c r="H12" s="11" t="n"/>
     </row>
-    <row r="13" ht="67.8" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+    <row r="13" ht="63" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>7éme (B)</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Arabe
 Yahya</t>
         </is>
       </c>
       <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 7éme (A) + 7éme (B)</t>
-        </is>
-      </c>
+      <c r="D13" s="12" t="n"/>
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Khouloud</t>
         </is>
@@ -5408,14 +4757,14 @@
       <c r="G13" s="11" t="n"/>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>15:30 - 17:00
+          <t>15:30-17:00
 Français
 Marwa</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="83" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+    <row r="14" ht="63" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>8éme (A)</t>
         </is>
@@ -5424,43 +4773,42 @@
       <c r="C14" s="10" t="n"/>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Arabe
 Awatef</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Français
 Nassima</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 فيزياء
-Melek
-⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
+Melek</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>17:30 - 19:00   ◆ Q-A
+          <t>17:30-19:00 Q-A
 SVT
 Sabrine</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>13:45 - 15:15
+          <t>13:45-15:15
 Math
 Hajer</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="83" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+    <row r="15" ht="63" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>8éme (B)</t>
         </is>
@@ -5468,108 +4816,77 @@
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Arabe
-Yahya
-⊕ 8éme (B) + 8éme (C)</t>
+Yahya</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Math
 Khouloud</t>
         </is>
       </c>
       <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>17:30-19:00 Q-A
+Anglais
+Imen Ben Lazrak</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>17:00-18:30
+Français
+Marwa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="63" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>8éme (C)</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>19:30-21:00
+Français
+Nabil</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>19:15-20:45
+Math
+Khouloud</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="11" t="n"/>
+    </row>
+    <row r="17" ht="63" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>9éme (A)</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>19:30-21:00
 فيزياء
-Melek
-⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-A
-Anglais
-Imen Ben Lazrak
-⊕ 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>17:00 - 18:30
-Français
-Marwa</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="83" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>8éme (C)</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-Arabe
-Yahya
-⊕ 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-Français
-Nabil</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45
-Math
-Khouloud</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 8éme (A) + 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-A
-Anglais
-Imen Ben Lazrak
-⊕ 8éme (B) + 8éme (C)</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="n"/>
-    </row>
-    <row r="17" ht="83" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>9éme (A)</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
+Melek</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Math
 Faouzi</t>
         </is>
@@ -5577,7 +4894,7 @@
       <c r="D17" s="10" t="n"/>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
@@ -5585,22 +4902,22 @@
       <c r="F17" s="10" t="n"/>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>16:30 - 18:00
+          <t>16:30-18:00
 Arabe
 Awatef</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Anglais
 Bassma</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="52.59999999999999" customHeight="1">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="10" t="n"/>
+    <row r="18" ht="63" customHeight="1">
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="16" t="n"/>
       <c r="C18" s="10" t="n"/>
       <c r="D18" s="10" t="n"/>
       <c r="E18" s="10" t="n"/>
@@ -5608,36 +4925,29 @@
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>15:30 - 17:00
+          <t>15:30-17:00
 Français
 Nassima</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="83" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="19" ht="63" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>9éme (B)</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
-        </is>
-      </c>
+      <c r="B19" s="16" t="n"/>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Arabe
 Yahya</t>
         </is>
@@ -5646,22 +4956,22 @@
       <c r="F19" s="10" t="n"/>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>17:30 - 19:00
+          <t>17:30-19:00
 Math
 Hajer</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>09:00 - 10:30
+          <t>09:00-10:30
 Anglais
 Bassma</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="67.8" customHeight="1">
-      <c r="A20" s="15" t="n"/>
-      <c r="B20" s="10" t="n"/>
+    <row r="20" ht="63" customHeight="1">
+      <c r="A20" s="17" t="n"/>
+      <c r="B20" s="16" t="n"/>
       <c r="C20" s="10" t="n"/>
       <c r="D20" s="10" t="n"/>
       <c r="E20" s="10" t="n"/>
@@ -5669,95 +4979,80 @@
       <c r="G20" s="11" t="n"/>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 18:30
-Français
-Nassima
-⊕ 9éme (B) + 9éme (C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="83" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
+          <t>17:00-18:30
+Français
+Nassima</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="63" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>9éme (C)</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00
-فيزياء
-Melek
-⊕ 9éme (A) + 9éme (B) + 9éme (C)</t>
-        </is>
-      </c>
+      <c r="B21" s="12" t="n"/>
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Anglais
 Saber</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Arabe
 Yahya</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Math
 Hajer</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>17:00 - 18:30
-Français
-Nassima
-⊕ 9éme (B) + 9éme (C)</t>
-        </is>
-      </c>
+      <c r="H21" s="12" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>CYCLE SECONDAIRE   (8 classes)</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="17" t="n"/>
-      <c r="G22" s="17" t="n"/>
-      <c r="H22" s="17" t="n"/>
-    </row>
-    <row r="23" ht="52.59999999999999" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="19" t="n"/>
+    </row>
+    <row r="23" ht="63" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>1ére (A)</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Français
 Nassima</t>
         </is>
@@ -5765,14 +5060,14 @@
       <c r="D23" s="10" t="n"/>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-A
+          <t>19:15-20:45 Q-A
 Anglais
 Imen Bennour</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>17:30 - 19:00
+          <t>17:30-19:00
 Arabe
 Najet</t>
         </is>
@@ -5780,14 +5075,14 @@
       <c r="G23" s="11" t="n"/>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>09:00 - 10:30
+          <t>09:00-10:30
 Physique
 Refka</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="52.59999999999999" customHeight="1">
-      <c r="A24" s="19" t="n"/>
+    <row r="24" ht="63" customHeight="1">
+      <c r="A24" s="17" t="n"/>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
@@ -5796,14 +5091,14 @@
       <c r="G24" s="11" t="n"/>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>13:00 - 14:30   ◆ Q-A
+          <t>13:00-14:30 Q-A
 SVT
 Imen Ghoumeme</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="52.59999999999999" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
+    <row r="25" ht="63" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>1ére (B)</t>
         </is>
@@ -5811,14 +5106,14 @@
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45
+          <t>19:15-20:45
 Français
 Nassima</t>
         </is>
@@ -5826,7 +5121,7 @@
       <c r="E25" s="10" t="n"/>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Arabe
 Najet</t>
         </is>
@@ -5834,14 +5129,14 @@
       <c r="G25" s="11" t="n"/>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Physique
 Refka</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="83" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
+    <row r="26" ht="63" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>2éme Eco</t>
         </is>
@@ -5849,144 +5144,114 @@
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-A
+          <t>19:15-20:45 Q-A
 Anglais
-Imen Bennour
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
+Imen Bennour</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Gestion
 Yassine</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>17:30 - 19:00   ◆ Q-A
-Français
-Nabil
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
+          <t>17:30-19:00 Q-A
+Français
+Nabil</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>15:30 - 17:00   ◆ Q-A
+          <t>15:30-17:00 Q-A
 Histoire
 Abdelwaheb</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>09:00 - 10:30
+          <t>09:00-10:30
 Eco
 Rym</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="83" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
+    <row r="27" ht="63" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>2éme SCE</t>
         </is>
       </c>
       <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45   ◆ Q-A
-Anglais
-Imen Bennour
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
-        </is>
-      </c>
+      <c r="C27" s="16" t="n"/>
       <c r="D27" s="10" t="n"/>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-A
-Français
-Nabil
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
-        </is>
-      </c>
+      <c r="F27" s="16" t="n"/>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>16:00 - 17:30
+          <t>16:00-17:30
 SVT
 Rym</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>12:00 - 13:30
+          <t>12:00-13:30
 Physique
 Refka</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="83" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
+    <row r="28" ht="63" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>2éme INFO</t>
         </is>
       </c>
       <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45   ◆ Q-A
-Anglais
-Imen Bennour
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
-        </is>
-      </c>
+      <c r="C28" s="16" t="n"/>
       <c r="D28" s="10" t="n"/>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-A
-Français
-Nabil
-⊕ 2éme Eco + 2éme SCE + 2éme INFO</t>
-        </is>
-      </c>
+      <c r="F28" s="12" t="n"/>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 19:00
+          <t>17:00-19:00
 Informatique
 Aymen</t>
         </is>
       </c>
       <c r="H28" s="11" t="n"/>
     </row>
-    <row r="29" ht="52.59999999999999" customHeight="1">
-      <c r="A29" s="19" t="n"/>
+    <row r="29" ht="63" customHeight="1">
+      <c r="A29" s="17" t="n"/>
       <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
+      <c r="C29" s="12" t="n"/>
       <c r="D29" s="10" t="n"/>
       <c r="E29" s="10" t="n"/>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Math
 Haythem</t>
         </is>
@@ -5994,8 +5259,8 @@
       <c r="G29" s="11" t="n"/>
       <c r="H29" s="11" t="n"/>
     </row>
-    <row r="30" ht="83" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+    <row r="30" ht="63" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>3éme Eco</t>
         </is>
@@ -6004,67 +5269,65 @@
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Gestion
 Yassine</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00   ◆ Q-A
+          <t>19:30-21:00 Q-A
 Arabe
-Najet
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+Najet</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30   ◆ Q-A
-Français
-Nabil
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
+          <t>19:00-20:30 Q-A
+Français
+Nabil</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>17:00 - 18:30   ◆ Q-A
+          <t>17:00-18:30 Q-A
 Histoire
 Abdelwaheb</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Eco
 Rym</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="52.59999999999999" customHeight="1">
-      <c r="A31" s="19" t="n"/>
+    <row r="31" ht="63" customHeight="1">
+      <c r="A31" s="17" t="n"/>
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="10" t="n"/>
       <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
       <c r="G31" s="11" t="n"/>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>14:00 - 15:30
+          <t>14:00-15:30
 Math
 Lotfi</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="83" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="32" ht="63" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>3éme INFO</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>15:30 - 17:30
+          <t>15:30-17:30
 STI
 Aymen</t>
         </is>
@@ -6072,349 +5335,285 @@
       <c r="C32" s="10" t="n"/>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00   ◆ Q-A
-Arabe
-Najet
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>19:00 - 20:30   ◆ Q-A
-Français
-Nabil
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
-        </is>
-      </c>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>15:00 - 17:00
+          <t>15:00-17:00
 ALGO
 Aymen</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>12:00 - 13:30
+          <t>12:00-13:30
 Math
 Lotfi</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="83" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="33" ht="63" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>3éme SCE</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 Math
 Lotfi</t>
         </is>
       </c>
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>19:30 - 21:00   ◆ Q-A
-Arabe
-Najet
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>19:00 - 20:30   ◆ Q-A
-Français
-Nabil
-⊕ 3éme Eco + 3éme INFO + 3éme SCE</t>
-        </is>
-      </c>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>17:30 - 19:00
+          <t>17:30-19:00
 SVT
 Rym</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Physique
 Sondes</t>
         </is>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>CYCLE BAC   (3 classes)</t>
         </is>
       </c>
-      <c r="B34" s="21" t="n"/>
-      <c r="C34" s="21" t="n"/>
-      <c r="D34" s="21" t="n"/>
-      <c r="E34" s="21" t="n"/>
-      <c r="F34" s="21" t="n"/>
-      <c r="G34" s="21" t="n"/>
-      <c r="H34" s="21" t="n"/>
-    </row>
-    <row r="35" ht="83" customHeight="1">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="22" t="n"/>
+      <c r="H34" s="22" t="n"/>
+    </row>
+    <row r="35" ht="63" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>Bac Eco</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 Gestion
 Yassine</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-A   ◆ OPTION
+          <t>19:15-20:45 Q-A OPT
 Espagnol
-Imen
-⊕ Bac Eco + Bac SCE</t>
+Imen</t>
         </is>
       </c>
       <c r="D35" s="10" t="n"/>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 20:30   ◆ Q-A
+          <t>19:00-20:30 Q-A
 Philo
-Fayssel
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
+Fayssel</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>17:30 - 19:00   ◆ Q-A
+          <t>17:30-19:00 Q-A
 Anglais
-Khaled
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
+Khaled</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>18:30 - 20:00   ◆ Q-A
+          <t>18:30-20:00 Q-A
 Histoire
 Abdelwaheb</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>10:30 - 12:00
+          <t>10:30-12:00
 Math
 Lotfi</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="52.59999999999999" customHeight="1">
-      <c r="A36" s="23" t="n"/>
+    <row r="36" ht="63" customHeight="1">
+      <c r="A36" s="17" t="n"/>
       <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
+      <c r="C36" s="16" t="n"/>
       <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
       <c r="G36" s="11" t="n"/>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>12:30 - 14:30
+          <t>12:30-14:30
 Eco
 Rym</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="83" customHeight="1">
-      <c r="A37" s="22" t="inlineStr">
+    <row r="37" ht="63" customHeight="1">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>Bac SCE</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 Physique
 Sondes</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45   ◆ Q-A   ◆ OPTION
-Espagnol
-Imen
-⊕ Bac Eco + Bac SCE</t>
-        </is>
-      </c>
+      <c r="C37" s="12" t="n"/>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 Math
 Ahmed</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>19:00 - 20:30   ◆ Q-A
-Philo
-Fayssel
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-A
-Anglais
-Khaled
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
-        </is>
-      </c>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>19:00 - 20:30
+          <t>19:00-20:30
 SVT
 Rym</t>
         </is>
       </c>
       <c r="H37" s="11" t="n"/>
     </row>
-    <row r="38" ht="83" customHeight="1">
-      <c r="A38" s="23" t="n"/>
+    <row r="38" ht="63" customHeight="1">
+      <c r="A38" s="17" t="n"/>
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>19:15 - 20:45   ◆ Q-A   ◆ OPTION
+          <t>19:15-20:45 Q-A OPT
 Italien
-Amel
-⊕ Bac SCE + Bac INFO</t>
+Amel</t>
         </is>
       </c>
       <c r="D38" s="10" t="n"/>
-      <c r="E38" s="10" t="n"/>
-      <c r="F38" s="10" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
       <c r="G38" s="11" t="n"/>
       <c r="H38" s="11" t="n"/>
     </row>
-    <row r="39" ht="83" customHeight="1">
-      <c r="A39" s="22" t="inlineStr">
+    <row r="39" ht="63" customHeight="1">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>Bac INFO</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>19:30 - 21:00
+          <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>19:15 - 20:45   ◆ Q-A   ◆ OPTION
-Italien
-Amel
-⊕ Bac SCE + Bac INFO</t>
-        </is>
-      </c>
+      <c r="C39" s="12" t="n"/>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>19:00 - 20:30   ◆ Q-A
-Philo
-Fayssel
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>17:30 - 19:00   ◆ Q-A
-Anglais
-Khaled
-⊕ Bac Eco + Bac SCE + Bac INFO</t>
-        </is>
-      </c>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="12" t="n"/>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>19:00 - 21:00
+          <t>19:00-21:00
 ALGO
 Heni</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>15:30 - 17:00
+          <t>15:30-17:00
 Math
 Lotfi</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="30">
+    <mergeCell ref="F35:F39"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="F30:F33"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="E30:E33"/>
     <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A28:A29"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A10:H10"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="E35:E39"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="C15:C16"/>
     <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A34:H34"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:H39">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Arabe"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"عربية"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Français"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Anglais"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Espagnol"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Italien"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Math"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"رياضيات"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
+    <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Physique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"فيزياء"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"SVT"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Éveil scientifique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"إيقاظ علمي"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="5">
+    <cfRule type="expression" priority="6" dxfId="5" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Histoire"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Géographie"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Philo"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="6">
+    <cfRule type="expression" priority="7" dxfId="6" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Eco"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Gestion"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="7">
+    <cfRule type="expression" priority="8" dxfId="7" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Informatique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"ALGO"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"STI"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" dxfId="8">
-      <formula>ISNUMBER(SEARCH("◆ PONCTUEL",B5))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="10" dxfId="9">
-      <formula>ISNUMBER(SEARCH("◆ Q-",B5))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="11" dxfId="10" stopIfTrue="1">
+    <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
       <formula>LEN(B5)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/livrables/RS_2026-2027_Octobre_seul.xlsx
+++ b/livrables/RS_2026-2027_Octobre_seul.xlsx
@@ -308,60 +308,123 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FBE3DC"/>
+          <fgColor rgb="0095B5EC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00DCE8F7"/>
+          <fgColor rgb="00ECDC95"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00DFF0E4"/>
+          <fgColor rgb="00CBF3E2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FDF0D5"/>
+          <fgColor rgb="00ECF3CB"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00E2E6F5"/>
+          <fgColor rgb="00AAF6BB"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00F3E1EE"/>
+          <fgColor rgb="0095ECE6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FAE6CF"/>
+          <fgColor rgb="00CFF6AA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00DCEFF2"/>
+          <fgColor rgb="00F6AAD8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D195EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00CBCCF3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F6CDAA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00AAE0F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C4AAF6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F6AABD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F3CBF1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00A0EC95"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F3CFCB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -765,7 +828,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Une case = une séance : horaire / matière / enseignant.   Couleur = famille de matières.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.</t>
+          <t>Une case = une séance : horaire / matière / enseignant.   Chaque matière a sa couleur.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1888,30 +1951,57 @@
   </mergeCells>
   <conditionalFormatting sqref="B5:H37">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Math"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"رياضيات"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Physique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"فيزياء"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Français"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Arabe"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"عربية"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Français"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Anglais"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Espagnol"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Italien"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Math"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"رياضيات"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
     <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Physique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"فيزياء"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"SVT"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Éveil scientifique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"إيقاظ علمي"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Anglais"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="5" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Histoire"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Géographie"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Philo"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"SVT"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="7" dxfId="6" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Eco"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Gestion"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Éveil scientifique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"إيقاظ علمي"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="8" dxfId="7" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Informatique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"ALGO"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"STI"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Histoire"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Géographie"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="9" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Philo"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" dxfId="10" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Eco"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="11" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Gestion"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="13" dxfId="12" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Informatique"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="13" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"ALGO"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="14" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"STI"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="16" dxfId="15" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Espagnol"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="17" dxfId="16" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Italien"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" dxfId="17" stopIfTrue="1">
       <formula>LEN(B5)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1971,7 +2061,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Une case = une séance : horaire / matière / enseignant.   Couleur = famille de matières.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.</t>
+          <t>Une case = une séance : horaire / matière / enseignant.   Chaque matière a sa couleur.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3142,30 +3232,57 @@
   </mergeCells>
   <conditionalFormatting sqref="B5:H39">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Math"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"رياضيات"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Physique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"فيزياء"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Français"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Arabe"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"عربية"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Français"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Anglais"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Espagnol"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Italien"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Math"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"رياضيات"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
     <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Physique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"فيزياء"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"SVT"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Éveil scientifique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"إيقاظ علمي"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Anglais"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="5" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Histoire"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Géographie"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Philo"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"SVT"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="7" dxfId="6" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Eco"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Gestion"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Éveil scientifique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"إيقاظ علمي"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="8" dxfId="7" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Informatique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"ALGO"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"STI"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Histoire"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Géographie"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="9" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Philo"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" dxfId="10" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Eco"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="11" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Gestion"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="13" dxfId="12" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Informatique"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="13" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"ALGO"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="14" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"STI"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="16" dxfId="15" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Espagnol"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="17" dxfId="16" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Italien"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" dxfId="17" stopIfTrue="1">
       <formula>LEN(B5)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3225,7 +3342,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Une case = une séance : horaire / matière / enseignant.   Couleur = famille de matières.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.</t>
+          <t>Une case = une séance : horaire / matière / enseignant.   Chaque matière a sa couleur.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4348,30 +4465,57 @@
   </mergeCells>
   <conditionalFormatting sqref="B5:H37">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Math"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"رياضيات"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Physique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"فيزياء"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Français"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Arabe"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"عربية"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Français"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Anglais"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Espagnol"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Italien"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Math"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"رياضيات"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
     <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Physique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"فيزياء"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"SVT"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Éveil scientifique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"إيقاظ علمي"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Anglais"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="5" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Histoire"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Géographie"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Philo"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"SVT"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="7" dxfId="6" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Eco"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Gestion"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Éveil scientifique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"إيقاظ علمي"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="8" dxfId="7" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Informatique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"ALGO"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"STI"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Histoire"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Géographie"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="9" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Philo"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" dxfId="10" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Eco"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="11" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Gestion"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="13" dxfId="12" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Informatique"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="13" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"ALGO"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="14" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"STI"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="16" dxfId="15" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Espagnol"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="17" dxfId="16" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Italien"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" dxfId="17" stopIfTrue="1">
       <formula>LEN(B5)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4431,7 +4575,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Une case = une séance : horaire / matière / enseignant.   Couleur = famille de matières.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.</t>
+          <t>Une case = une séance : horaire / matière / enseignant.   Chaque matière a sa couleur.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5590,30 +5734,57 @@
   </mergeCells>
   <conditionalFormatting sqref="B5:H39">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Math"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"رياضيات"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Physique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"فيزياء"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Français"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
       <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Arabe"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"عربية"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Français"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Anglais"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Espagnol"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Italien"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Math"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"رياضيات"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
     <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Physique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"فيزياء"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"SVT"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Éveil scientifique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"إيقاظ علمي"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Anglais"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="5" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Histoire"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Géographie"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Philo"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"SVT"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="7" dxfId="6" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Eco"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"Gestion"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Éveil scientifique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"إيقاظ علمي"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="8" dxfId="7" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Informatique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"ALGO"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"STI"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Histoire"&amp;CHAR(10),B5)))&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Géographie"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="9" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Philo"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" dxfId="10" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Eco"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="11" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Gestion"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="13" dxfId="12" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Informatique"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="13" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"ALGO"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="14" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"STI"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="16" dxfId="15" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Espagnol"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="17" dxfId="16" stopIfTrue="1">
+      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Italien"&amp;CHAR(10),B5)))&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" dxfId="17" stopIfTrue="1">
       <formula>LEN(B5)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/livrables/RS_2026-2027_Octobre_seul.xlsx
+++ b/livrables/RS_2026-2027_Octobre_seul.xlsx
@@ -67,7 +67,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
@@ -96,12 +96,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00F5F7FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDFAF4"/>
+        <fgColor rgb="00F2F0EA"/>
       </patternFill>
     </fill>
     <fill>
@@ -142,6 +142,91 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEEBF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECF3CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0095B5EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CBF3E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFF6AA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00AAF6BB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECDC95"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0095ECE6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00AAE0F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D195EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6CDAA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C4AAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A0EC95"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CBCCF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3CBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3CFCB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6AABD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6AAD8"/>
       </patternFill>
     </fill>
   </fills>
@@ -251,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -274,10 +359,25 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -288,6 +388,12 @@
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -297,6 +403,33 @@
     <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -304,134 +437,53 @@
     <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="0095B5EC"/>
+          <fgColor rgb="00F5A7A0"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00ECDC95"/>
+          <fgColor rgb="00F7D154"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00CBF3E2"/>
+          <fgColor rgb="00C9A0DC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00ECF3CB"/>
+          <fgColor rgb="00F9C784"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00AAF6BB"/>
+          <fgColor rgb="008FC7E8"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="0095ECE6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00CFF6AA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F6AAD8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D195EC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00CBCCF3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F6CDAA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00AAE0F6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C4AAF6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F6AABD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F3CBF1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00A0EC95"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F3CFCB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F5F7FA"/>
+          <fgColor rgb="009FE0C8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -828,7 +880,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Une case = une séance : horaire / matière / enseignant.   Chaque matière a sa couleur.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.</t>
+          <t>Une case = une séance : horaire / matière / enseignant.   Chaque matière a sa couleur.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.   Les couleurs sont modifiables à la main ; seul un statut ⚑ les remplace.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -915,24 +967,24 @@
 Lobna</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 رياضيات
 Bassma</t>
         </is>
       </c>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>16:00-17:30
 Français
 Hend</t>
         </is>
       </c>
-      <c r="H6" s="11" t="n"/>
+      <c r="H6" s="14" t="n"/>
     </row>
     <row r="7" ht="63" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -940,7 +992,7 @@
           <t>5éme</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n"/>
+      <c r="B7" s="11" t="n"/>
       <c r="C7" s="10" t="inlineStr">
         <is>
           <t>19:00-21:00
@@ -948,29 +1000,29 @@
 Lobna</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 رياضيات
 Bassma</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>19:00-20:30 Q-B
 إيقاظ علمي
 Bassma</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>18:00-19:30
 Français
 Hend</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>10:30-12:00 Q-B
 Anglais
@@ -984,37 +1036,37 @@
           <t>6éme Pilote (A)</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>19:00-20:30
 Français
 Hend</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 رياضيات
 Noura</t>
         </is>
       </c>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>19:30-21:00
 إيقاظ علمي
 Noura</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>19:00-21:00
 عربية
 Lobna</t>
         </is>
       </c>
-      <c r="H8" s="11" t="n"/>
+      <c r="H8" s="14" t="n"/>
     </row>
     <row r="9" ht="63" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -1022,77 +1074,77 @@
           <t>6éme (B)</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>19:00-20:30
 Français
 Hend</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 رياضيات
 Noura</t>
         </is>
       </c>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>17:00-19:00
 عربية
 Lobna</t>
         </is>
       </c>
-      <c r="H9" s="11" t="n"/>
+      <c r="H9" s="14" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>CYCLE COLLÈGE   (8 classes)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="14" t="n"/>
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
     </row>
     <row r="11" ht="63" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>7éme (A)</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 فيزياء
 Melek</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>18:00-19:30
 Math
 Khouloud</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>18:00-19:30
 Arabe
 Awatef</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>14:00-15:30
 Français
@@ -1101,7 +1153,7 @@
       </c>
     </row>
     <row r="12" ht="63" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>7éme (B)</t>
         </is>
@@ -1113,30 +1165,30 @@
 Yahya</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>19:00-20:30 Q-B
 Anglais
 Imen Ben Lazrak</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Khouloud</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>16:00-17:30 Q-B
 SVT
 Sabrine</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t>15:30-17:00
 Français
@@ -1145,13 +1197,13 @@
       </c>
     </row>
     <row r="13" ht="63" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>8éme (A)</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
       <c r="D13" s="10" t="inlineStr">
         <is>
           <t>19:00-20:30
@@ -1159,28 +1211,28 @@
 Awatef</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>19:15-20:45
 Français
 Nassima</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 فيزياء
 Melek</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>17:30-19:00 Q-B
 Anglais
 Imen Ben Lazrak</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>13:45-15:15
 Math
@@ -1189,12 +1241,12 @@
       </c>
     </row>
     <row r="14" ht="63" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>8éme (B)</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n"/>
+      <c r="B14" s="11" t="n"/>
       <c r="C14" s="10" t="inlineStr">
         <is>
           <t>19:30-21:00
@@ -1202,23 +1254,23 @@
 Yahya</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>19:15-20:45
 Math
 Khouloud</t>
         </is>
       </c>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>17:30-19:00 Q-B
 SVT
 Sabrine</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t>17:00-18:30
 Français
@@ -1227,68 +1279,68 @@
       </c>
     </row>
     <row r="15" ht="63" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>8éme (C)</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>19:30-21:00
 Français
 Nabil</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>19:15-20:45
 Math
 Khouloud</t>
         </is>
       </c>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="11" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="14" t="n"/>
     </row>
     <row r="16" ht="63" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>9éme (A)</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 فيزياء
 Melek</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>19:00-20:30
 Math
 Faouzi</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>16:30-18:00
 Arabe
 Awatef</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t>10:30-12:00
 Anglais
@@ -1297,14 +1349,14 @@
       </c>
     </row>
     <row r="17" ht="63" customHeight="1">
-      <c r="A17" s="17" t="n"/>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="A17" s="24" t="n"/>
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>15:30-17:00
 Français
@@ -1313,13 +1365,13 @@
       </c>
     </row>
     <row r="18" ht="63" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>9éme (B)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>19:15-20:45
 SVT
@@ -1333,16 +1385,16 @@
 Yahya</t>
         </is>
       </c>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>17:30-19:00
 Math
 Hajer</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr">
         <is>
           <t>09:00-10:30
 Anglais
@@ -1351,14 +1403,14 @@
       </c>
     </row>
     <row r="19" ht="63" customHeight="1">
-      <c r="A19" s="17" t="n"/>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="A19" s="24" t="n"/>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="13" t="inlineStr">
         <is>
           <t>17:00-18:30
 Français
@@ -1367,21 +1419,21 @@
       </c>
     </row>
     <row r="20" ht="63" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>9éme (C)</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>19:30-21:00
 Anglais
@@ -1395,51 +1447,51 @@
 Yahya</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>19:00-20:30
 Math
 Hajer</t>
         </is>
       </c>
-      <c r="H20" s="12" t="n"/>
+      <c r="H20" s="17" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>CYCLE SECONDAIRE   (8 classes)</t>
         </is>
       </c>
-      <c r="B21" s="19" t="n"/>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="19" t="n"/>
-      <c r="F21" s="19" t="n"/>
-      <c r="G21" s="19" t="n"/>
-      <c r="H21" s="19" t="n"/>
+      <c r="B21" s="26" t="n"/>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="26" t="n"/>
+      <c r="E21" s="26" t="n"/>
+      <c r="F21" s="26" t="n"/>
+      <c r="G21" s="26" t="n"/>
+      <c r="H21" s="26" t="n"/>
     </row>
     <row r="22" ht="63" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>1ére (A)</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>19:15-20:45
 Français
 Nassima</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
       <c r="F22" s="10" t="inlineStr">
         <is>
           <t>17:30-19:00
@@ -1447,8 +1499,8 @@
 Najet</t>
         </is>
       </c>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>09:00-10:30
 Physique
@@ -1457,27 +1509,27 @@
       </c>
     </row>
     <row r="23" ht="63" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>1ére (B)</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>19:15-20:45
 Français
 Nassima</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>19:15-20:45 Q-B
 Anglais
@@ -1491,8 +1543,8 @@
 Najet</t>
         </is>
       </c>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>10:30-12:00
 Physique
@@ -1501,14 +1553,14 @@
       </c>
     </row>
     <row r="24" ht="63" customHeight="1">
-      <c r="A24" s="17" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>13:00-14:30 Q-B
 SVT
@@ -1517,12 +1569,12 @@
       </c>
     </row>
     <row r="25" ht="63" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>2éme Eco</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
+      <c r="B25" s="11" t="n"/>
       <c r="C25" s="10" t="inlineStr">
         <is>
           <t>19:30-21:00 Q-B
@@ -1530,29 +1582,29 @@
 Najet</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="28" t="inlineStr">
         <is>
           <t>19:00-20:30
 Gestion
 Yassine</t>
         </is>
       </c>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="29" t="inlineStr">
         <is>
           <t>15:30-17:00 Q-B
 Géographie
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="30" t="inlineStr">
         <is>
           <t>09:00-10:30
 Eco
@@ -1561,30 +1613,30 @@
       </c>
     </row>
     <row r="26" ht="63" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>2éme SCE</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>16:00-17:30
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>12:00-13:30
 Physique
@@ -1593,80 +1645,80 @@
       </c>
     </row>
     <row r="27" ht="63" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>2éme INFO</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="31" t="inlineStr">
         <is>
           <t>17:00-19:00
 Informatique
 Aymen</t>
         </is>
       </c>
-      <c r="H27" s="11" t="n"/>
+      <c r="H27" s="14" t="n"/>
     </row>
     <row r="28" ht="63" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>3éme Eco</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="32" t="inlineStr">
         <is>
           <t>19:15-20:45 Q-B OPT
 Espagnol
 Imen</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="28" t="inlineStr">
         <is>
           <t>19:00-20:30
 Gestion
 Yassine</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>19:00-20:30 Q-B
 Philo
 Fayssel</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>17:30-19:00 Q-B
 Anglais
 Khaled</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="29" t="inlineStr">
         <is>
           <t>17:00-18:30 Q-B
 Géographie
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="30" t="inlineStr">
         <is>
           <t>10:30-12:00
 Eco
@@ -1675,14 +1727,14 @@
       </c>
     </row>
     <row r="29" ht="63" customHeight="1">
-      <c r="A29" s="17" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="A29" s="24" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>14:00-15:30
 Math
@@ -1691,36 +1743,36 @@
       </c>
     </row>
     <row r="30" ht="63" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>3éme INFO</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="34" t="inlineStr">
         <is>
           <t>15:30-17:30
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="35" t="inlineStr">
         <is>
           <t>15:00-17:00
 ALGO
 Aymen</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>12:00-13:30
 Math
@@ -1729,46 +1781,46 @@
       </c>
     </row>
     <row r="31" ht="63" customHeight="1">
-      <c r="A31" s="17" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="A31" s="24" t="n"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>19:15-20:45 Q-B OPT
 Italien
 Amel</t>
         </is>
       </c>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="23" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
     </row>
     <row r="32" ht="63" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>3éme SCE</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>19:00-20:30
 Math
 Lotfi</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n"/>
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>17:30-19:00
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>10:30-12:00
 Physique
@@ -1777,34 +1829,34 @@
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="37" t="inlineStr">
         <is>
           <t>CYCLE BAC   (3 classes)</t>
         </is>
       </c>
-      <c r="B33" s="22" t="n"/>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="22" t="n"/>
-      <c r="E33" s="22" t="n"/>
-      <c r="F33" s="22" t="n"/>
-      <c r="G33" s="22" t="n"/>
-      <c r="H33" s="22" t="n"/>
+      <c r="B33" s="38" t="n"/>
+      <c r="C33" s="38" t="n"/>
+      <c r="D33" s="38" t="n"/>
+      <c r="E33" s="38" t="n"/>
+      <c r="F33" s="38" t="n"/>
+      <c r="G33" s="38" t="n"/>
+      <c r="H33" s="38" t="n"/>
     </row>
     <row r="34" ht="63" customHeight="1">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="39" t="inlineStr">
         <is>
           <t>Bac Eco</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>19:00-21:00
 Gestion
 Yassine</t>
         </is>
       </c>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
       <c r="E34" s="10" t="inlineStr">
         <is>
           <t>19:30-21:00 Q-B
@@ -1812,21 +1864,21 @@
 Najet</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>17:30-19:00 Q-B
 Français
 Nabil</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="29" t="inlineStr">
         <is>
           <t>18:30-20:00 Q-B
 Géographie
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>10:30-12:00
 Math
@@ -1835,14 +1887,14 @@
       </c>
     </row>
     <row r="35" ht="63" customHeight="1">
-      <c r="A35" s="17" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="A35" s="24" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="14" t="n"/>
+      <c r="H35" s="30" t="inlineStr">
         <is>
           <t>12:30-14:30
 Eco
@@ -1851,68 +1903,68 @@
       </c>
     </row>
     <row r="36" ht="63" customHeight="1">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="A36" s="39" t="inlineStr">
         <is>
           <t>Bac SCE</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>19:00-21:00
 Physique
 Sondes</t>
         </is>
       </c>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 Math
 Ahmed</t>
         </is>
       </c>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="E36" s="23" t="n"/>
+      <c r="F36" s="23" t="n"/>
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>19:00-20:30
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H36" s="11" t="n"/>
+      <c r="H36" s="14" t="n"/>
     </row>
     <row r="37" ht="63" customHeight="1">
-      <c r="A37" s="23" t="inlineStr">
+      <c r="A37" s="39" t="inlineStr">
         <is>
           <t>Bac INFO</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="34" t="inlineStr">
         <is>
           <t>19:00-21:00
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
+      <c r="G37" s="35" t="inlineStr">
         <is>
           <t>19:00-21:00
 ALGO
 Heni</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>15:30-17:00
 Math
@@ -1951,58 +2003,22 @@
   </mergeCells>
   <conditionalFormatting sqref="B5:H37">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Math"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"رياضيات"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Annulé",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Physique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"فيزياء"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Examen / Devoir",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Français"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Rattrapage",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Arabe"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"عربية"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ À confirmer",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Anglais"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Changement de salle",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="5" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"SVT"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="7" dxfId="6" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Éveil scientifique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"إيقاظ علمي"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="8" dxfId="7" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Histoire"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Géographie"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="10" dxfId="9" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Philo"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="11" dxfId="10" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Eco"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="12" dxfId="11" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Gestion"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="13" dxfId="12" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Informatique"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="14" dxfId="13" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"ALGO"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="15" dxfId="14" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"STI"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="16" dxfId="15" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Espagnol"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="17" dxfId="16" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Italien"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="18" dxfId="17" stopIfTrue="1">
-      <formula>LEN(B5)=0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Séance en ligne",B5))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1" gridLines="0"/>
@@ -2061,7 +2077,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Une case = une séance : horaire / matière / enseignant.   Chaque matière a sa couleur.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.</t>
+          <t>Une case = une séance : horaire / matière / enseignant.   Chaque matière a sa couleur.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.   Les couleurs sont modifiables à la main ; seul un statut ⚑ les remplace.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2148,30 +2164,30 @@
 Lobna</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 رياضيات
 Bassma</t>
         </is>
       </c>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>19:00-20:30 Q-A
 إيقاظ علمي
 Bassma</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>16:00-17:30
 Français
 Hend</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t>10:30-12:00 Q-A
 Anglais
@@ -2185,7 +2201,7 @@
           <t>5éme</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n"/>
+      <c r="B7" s="11" t="n"/>
       <c r="C7" s="10" t="inlineStr">
         <is>
           <t>19:00-21:00
@@ -2193,8 +2209,8 @@
 Lobna</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 رياضيات
@@ -2202,15 +2218,15 @@
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F7" s="10" t="n"/>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>18:00-19:30
 Français
 Hend</t>
         </is>
       </c>
-      <c r="H7" s="11" t="n"/>
+      <c r="H7" s="14" t="n"/>
     </row>
     <row r="8" ht="63" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -2218,37 +2234,37 @@
           <t>6éme Pilote (A)</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>19:00-20:30
 Français
 Hend</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 رياضيات
 Noura</t>
         </is>
       </c>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>19:30-21:00
 إيقاظ علمي
 Noura</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>19:00-21:00
 عربية
 Lobna</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>12:00-13:30 Q-A
 Anglais
@@ -2262,16 +2278,16 @@
           <t>6éme (B)</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>19:00-20:30
 Français
 Hend</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 رياضيات
@@ -2279,67 +2295,67 @@
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>17:00-19:00
 عربية
 Lobna</t>
         </is>
       </c>
-      <c r="H9" s="12" t="n"/>
+      <c r="H9" s="17" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>CYCLE COLLÈGE   (8 classes)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="14" t="n"/>
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
     </row>
     <row r="11" ht="63" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>7éme (A)</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>19:00-20:30 Q-A
 Anglais
 Imen Ben Lazrak</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 فيزياء
 Melek</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>18:00-19:30
 Math
 Khouloud</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>16:00-17:30 Q-A
 SVT
 Sabrine</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>14:00-15:30
 Français
@@ -2348,23 +2364,23 @@
       </c>
     </row>
     <row r="12" ht="63" customHeight="1">
-      <c r="A12" s="17" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="A12" s="24" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>18:00-19:30
 Arabe
 Awatef</t>
         </is>
       </c>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="14" t="n"/>
     </row>
     <row r="13" ht="63" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>7éme (B)</t>
         </is>
@@ -2376,18 +2392,18 @@
 Yahya</t>
         </is>
       </c>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Khouloud</t>
         </is>
       </c>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t>15:30-17:00
 Français
@@ -2396,13 +2412,13 @@
       </c>
     </row>
     <row r="14" ht="99" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>8éme (A)</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
       <c r="D14" s="10" t="inlineStr">
         <is>
           <t>19:00-20:30
@@ -2410,7 +2426,7 @@
 Awatef</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>19:15-20:45
 Français
@@ -2418,21 +2434,21 @@
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 فيزياء
 Melek</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>17:30-19:00 Q-A
 SVT
 Sabrine</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>13:45-15:15
 Math
@@ -2441,12 +2457,12 @@
       </c>
     </row>
     <row r="15" ht="63" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>8éme (B)</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n"/>
+      <c r="B15" s="11" t="n"/>
       <c r="C15" s="10" t="inlineStr">
         <is>
           <t>19:30-21:00
@@ -2454,23 +2470,23 @@
 Yahya</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>19:15-20:45
 Math
 Khouloud</t>
         </is>
       </c>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>17:30-19:00 Q-A
 Anglais
 Imen Ben Lazrak</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t>17:00-18:30
 Français
@@ -2479,21 +2495,21 @@
       </c>
     </row>
     <row r="16" ht="99" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>8éme (C)</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>19:30-21:00
 Français
 Nabil</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>19:15-20:45
 Math
@@ -2501,32 +2517,32 @@
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="11" t="n"/>
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="14" t="n"/>
     </row>
     <row r="17" ht="99" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>9éme (A)</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 فيزياء
 Melek</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>19:00-20:30
 Math
 Faouzi</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>19:15-20:45
 SVT
@@ -2534,15 +2550,15 @@
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>16:30-18:00
 Arabe
 Awatef</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>10:30-12:00
 Anglais
@@ -2551,14 +2567,14 @@
       </c>
     </row>
     <row r="18" ht="63" customHeight="1">
-      <c r="A18" s="17" t="n"/>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="A18" s="24" t="n"/>
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t>15:30-17:00
 Français
@@ -2567,13 +2583,13 @@
       </c>
     </row>
     <row r="19" ht="63" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>9éme (B)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>19:15-20:45
 SVT
@@ -2587,16 +2603,16 @@
 Yahya</t>
         </is>
       </c>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>17:30-19:00
 Math
 Hajer</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>09:00-10:30
 Anglais
@@ -2605,14 +2621,14 @@
       </c>
     </row>
     <row r="20" ht="63" customHeight="1">
-      <c r="A20" s="17" t="n"/>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="A20" s="24" t="n"/>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="13" t="inlineStr">
         <is>
           <t>17:00-18:30
 Français
@@ -2621,21 +2637,21 @@
       </c>
     </row>
     <row r="21" ht="99" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>9éme (C)</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>19:30-21:00
 Anglais
@@ -2650,51 +2666,51 @@
 Yahya</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>19:00-20:30
 Math
 Hajer</t>
         </is>
       </c>
-      <c r="H21" s="12" t="n"/>
+      <c r="H21" s="17" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>CYCLE SECONDAIRE   (8 classes)</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="19" t="n"/>
-      <c r="F22" s="19" t="n"/>
-      <c r="G22" s="19" t="n"/>
-      <c r="H22" s="19" t="n"/>
+      <c r="B22" s="26" t="n"/>
+      <c r="C22" s="26" t="n"/>
+      <c r="D22" s="26" t="n"/>
+      <c r="E22" s="26" t="n"/>
+      <c r="F22" s="26" t="n"/>
+      <c r="G22" s="26" t="n"/>
+      <c r="H22" s="26" t="n"/>
     </row>
     <row r="23" ht="99" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>1ére (A)</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>19:15-20:45
 Français
 Nassima</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>19:15-20:45 Q-A
 Anglais
@@ -2709,8 +2725,8 @@
 Najet</t>
         </is>
       </c>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>09:00-10:30
 Physique
@@ -2719,14 +2735,14 @@
       </c>
     </row>
     <row r="24" ht="63" customHeight="1">
-      <c r="A24" s="17" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>13:00-14:30 Q-A
 SVT
@@ -2735,27 +2751,27 @@
       </c>
     </row>
     <row r="25" ht="63" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>1ére (B)</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>19:15-20:45
 Français
 Nassima</t>
         </is>
       </c>
-      <c r="E25" s="10" t="n"/>
+      <c r="E25" s="11" t="n"/>
       <c r="F25" s="10" t="inlineStr">
         <is>
           <t>19:00-20:30
@@ -2763,8 +2779,8 @@
 Najet</t>
         </is>
       </c>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>10:30-12:00
 Physique
@@ -2773,27 +2789,27 @@
       </c>
     </row>
     <row r="26" ht="99" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>2éme Eco</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>19:15-20:45 Q-A
 Anglais
 Imen Bennour</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="28" t="inlineStr">
         <is>
           <t>19:00-20:30
 Gestion
@@ -2801,21 +2817,21 @@
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>17:30-19:00 Q-A
 Français
 Nabil</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="40" t="inlineStr">
         <is>
           <t>15:30-17:00 Q-A
 Histoire
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="30" t="inlineStr">
         <is>
           <t>09:00-10:30
 Eco
@@ -2824,15 +2840,15 @@
       </c>
     </row>
     <row r="27" ht="99" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>2éme SCE</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
@@ -2840,15 +2856,15 @@
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F27" s="16" t="n"/>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>16:00-17:30
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>12:00-13:30
 Physique
@@ -2857,15 +2873,15 @@
       </c>
     </row>
     <row r="28" ht="99" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>2éme INFO</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 Physique
@@ -2873,41 +2889,41 @@
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="31" t="inlineStr">
         <is>
           <t>17:00-19:00
 Informatique
 Aymen</t>
         </is>
       </c>
-      <c r="H28" s="11" t="n"/>
+      <c r="H28" s="14" t="n"/>
     </row>
     <row r="29" ht="63" customHeight="1">
-      <c r="A29" s="17" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="A29" s="24" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="14" t="n"/>
     </row>
     <row r="30" ht="63" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>3éme Eco</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="28" t="inlineStr">
         <is>
           <t>19:00-20:30
 Gestion
@@ -2922,21 +2938,21 @@
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>19:00-20:30 Q-A
 Français
 Nabil</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="40" t="inlineStr">
         <is>
           <t>17:00-18:30 Q-A
 Histoire
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="30" t="inlineStr">
         <is>
           <t>10:30-12:00
 Eco
@@ -2945,14 +2961,14 @@
       </c>
     </row>
     <row r="31" ht="63" customHeight="1">
-      <c r="A31" s="17" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="A31" s="24" t="n"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="23" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>14:00-15:30
 Math
@@ -2961,36 +2977,36 @@
       </c>
     </row>
     <row r="32" ht="63" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>3éme INFO</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="34" t="inlineStr">
         <is>
           <t>15:30-17:30
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="E32" s="23" t="n"/>
+      <c r="F32" s="23" t="n"/>
+      <c r="G32" s="35" t="inlineStr">
         <is>
           <t>15:00-17:00
 ALGO
 Aymen</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>12:00-13:30
 Math
@@ -2999,30 +3015,30 @@
       </c>
     </row>
     <row r="33" ht="63" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>3éme SCE</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>19:00-20:30
 Math
 Lotfi</t>
         </is>
       </c>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="12" t="n"/>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>17:30-19:00
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>10:30-12:00
 Physique
@@ -3031,41 +3047,41 @@
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="37" t="inlineStr">
         <is>
           <t>CYCLE BAC   (3 classes)</t>
         </is>
       </c>
-      <c r="B34" s="22" t="n"/>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="22" t="n"/>
-      <c r="E34" s="22" t="n"/>
-      <c r="F34" s="22" t="n"/>
-      <c r="G34" s="22" t="n"/>
-      <c r="H34" s="22" t="n"/>
+      <c r="B34" s="38" t="n"/>
+      <c r="C34" s="38" t="n"/>
+      <c r="D34" s="38" t="n"/>
+      <c r="E34" s="38" t="n"/>
+      <c r="F34" s="38" t="n"/>
+      <c r="G34" s="38" t="n"/>
+      <c r="H34" s="38" t="n"/>
     </row>
     <row r="35" ht="63" customHeight="1">
-      <c r="A35" s="23" t="inlineStr">
+      <c r="A35" s="39" t="inlineStr">
         <is>
           <t>Bac Eco</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>19:00-21:00
 Gestion
 Yassine</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C35" s="32" t="inlineStr">
         <is>
           <t>19:15-20:45 Q-A OPT
 Espagnol
 Imen</t>
         </is>
       </c>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="33" t="inlineStr">
         <is>
           <t>19:00-20:30 Q-A
 Philo
@@ -3073,21 +3089,21 @@
 Jour férié (Évacuation) — à confirmer</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>17:30-19:00 Q-A
 Anglais
 Khaled</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G35" s="40" t="inlineStr">
         <is>
           <t>18:30-20:00 Q-A
 Histoire
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>10:30-12:00
 Math
@@ -3096,14 +3112,14 @@
       </c>
     </row>
     <row r="36" ht="63" customHeight="1">
-      <c r="A36" s="17" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="A36" s="24" t="n"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="23" t="n"/>
+      <c r="F36" s="23" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="30" t="inlineStr">
         <is>
           <t>12:30-14:30
 Eco
@@ -3112,84 +3128,84 @@
       </c>
     </row>
     <row r="37" ht="63" customHeight="1">
-      <c r="A37" s="23" t="inlineStr">
+      <c r="A37" s="39" t="inlineStr">
         <is>
           <t>Bac SCE</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>19:00-21:00
 Physique
 Sondes</t>
         </is>
       </c>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 Math
 Ahmed</t>
         </is>
       </c>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="E37" s="23" t="n"/>
+      <c r="F37" s="23" t="n"/>
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>19:00-20:30
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H37" s="11" t="n"/>
+      <c r="H37" s="14" t="n"/>
     </row>
     <row r="38" ht="63" customHeight="1">
-      <c r="A38" s="17" t="n"/>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="A38" s="24" t="n"/>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="36" t="inlineStr">
         <is>
           <t>19:15-20:45 Q-A OPT
 Italien
 Amel</t>
         </is>
       </c>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
-      <c r="G38" s="11" t="n"/>
-      <c r="H38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="23" t="n"/>
+      <c r="F38" s="23" t="n"/>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="14" t="n"/>
     </row>
     <row r="39" ht="63" customHeight="1">
-      <c r="A39" s="23" t="inlineStr">
+      <c r="A39" s="39" t="inlineStr">
         <is>
           <t>Bac INFO</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="34" t="inlineStr">
         <is>
           <t>19:00-21:00
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n"/>
-      <c r="F39" s="12" t="n"/>
-      <c r="G39" s="11" t="inlineStr">
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
+      <c r="G39" s="35" t="inlineStr">
         <is>
           <t>19:00-21:00
 ALGO
 Heni</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>15:30-17:00
 Math
@@ -3232,58 +3248,22 @@
   </mergeCells>
   <conditionalFormatting sqref="B5:H39">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Math"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"رياضيات"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Annulé",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Physique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"فيزياء"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Examen / Devoir",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Français"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Rattrapage",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Arabe"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"عربية"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ À confirmer",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Anglais"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Changement de salle",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="5" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"SVT"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="7" dxfId="6" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Éveil scientifique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"إيقاظ علمي"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="8" dxfId="7" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Histoire"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Géographie"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="10" dxfId="9" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Philo"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="11" dxfId="10" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Eco"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="12" dxfId="11" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Gestion"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="13" dxfId="12" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Informatique"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="14" dxfId="13" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"ALGO"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="15" dxfId="14" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"STI"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="16" dxfId="15" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Espagnol"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="17" dxfId="16" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Italien"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="18" dxfId="17" stopIfTrue="1">
-      <formula>LEN(B5)=0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Séance en ligne",B5))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1" gridLines="0"/>
@@ -3342,7 +3322,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Une case = une séance : horaire / matière / enseignant.   Chaque matière a sa couleur.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.</t>
+          <t>Une case = une séance : horaire / matière / enseignant.   Chaque matière a sa couleur.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.   Les couleurs sont modifiables à la main ; seul un statut ⚑ les remplace.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3429,24 +3409,24 @@
 Lobna</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 رياضيات
 Bassma</t>
         </is>
       </c>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>16:00-17:30
 Français
 Hend</t>
         </is>
       </c>
-      <c r="H6" s="11" t="n"/>
+      <c r="H6" s="14" t="n"/>
     </row>
     <row r="7" ht="63" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -3454,7 +3434,7 @@
           <t>5éme</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n"/>
+      <c r="B7" s="11" t="n"/>
       <c r="C7" s="10" t="inlineStr">
         <is>
           <t>19:00-21:00
@@ -3462,29 +3442,29 @@
 Lobna</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 رياضيات
 Bassma</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>19:00-20:30 Q-B
 إيقاظ علمي
 Bassma</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>18:00-19:30
 Français
 Hend</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>10:30-12:00 Q-B
 Anglais
@@ -3498,37 +3478,37 @@
           <t>6éme Pilote (A)</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>19:00-20:30
 Français
 Hend</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 رياضيات
 Noura</t>
         </is>
       </c>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>19:30-21:00
 إيقاظ علمي
 Noura</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>19:00-21:00
 عربية
 Lobna</t>
         </is>
       </c>
-      <c r="H8" s="11" t="n"/>
+      <c r="H8" s="14" t="n"/>
     </row>
     <row r="9" ht="63" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -3536,77 +3516,77 @@
           <t>6éme (B)</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>19:00-20:30
 Français
 Hend</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 رياضيات
 Noura</t>
         </is>
       </c>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>17:00-19:00
 عربية
 Lobna</t>
         </is>
       </c>
-      <c r="H9" s="11" t="n"/>
+      <c r="H9" s="14" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>CYCLE COLLÈGE   (8 classes)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="14" t="n"/>
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
     </row>
     <row r="11" ht="63" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>7éme (A)</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 فيزياء
 Melek</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>18:00-19:30
 Math
 Khouloud</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>18:00-19:30
 Arabe
 Awatef</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>14:00-15:30
 Français
@@ -3615,7 +3595,7 @@
       </c>
     </row>
     <row r="12" ht="63" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>7éme (B)</t>
         </is>
@@ -3627,30 +3607,30 @@
 Yahya</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>19:00-20:30 Q-B
 Anglais
 Imen Ben Lazrak</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Khouloud</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>16:00-17:30 Q-B
 SVT
 Sabrine</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t>15:30-17:00
 Français
@@ -3659,13 +3639,13 @@
       </c>
     </row>
     <row r="13" ht="63" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>8éme (A)</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
       <c r="D13" s="10" t="inlineStr">
         <is>
           <t>19:00-20:30
@@ -3673,28 +3653,28 @@
 Awatef</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>19:15-20:45
 Français
 Nassima</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 فيزياء
 Melek</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>17:30-19:00 Q-B
 Anglais
 Imen Ben Lazrak</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>13:45-15:15
 Math
@@ -3703,12 +3683,12 @@
       </c>
     </row>
     <row r="14" ht="63" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>8éme (B)</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n"/>
+      <c r="B14" s="11" t="n"/>
       <c r="C14" s="10" t="inlineStr">
         <is>
           <t>19:30-21:00
@@ -3716,23 +3696,23 @@
 Yahya</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>19:15-20:45
 Math
 Khouloud</t>
         </is>
       </c>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>17:30-19:00 Q-B
 SVT
 Sabrine</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t>17:00-18:30
 Français
@@ -3741,68 +3721,68 @@
       </c>
     </row>
     <row r="15" ht="63" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>8éme (C)</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>19:30-21:00
 Français
 Nabil</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>19:15-20:45
 Math
 Khouloud</t>
         </is>
       </c>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="11" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="14" t="n"/>
     </row>
     <row r="16" ht="63" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>9éme (A)</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 فيزياء
 Melek</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>19:00-20:30
 Math
 Faouzi</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>16:30-18:00
 Arabe
 Awatef</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t>10:30-12:00
 Anglais
@@ -3811,14 +3791,14 @@
       </c>
     </row>
     <row r="17" ht="63" customHeight="1">
-      <c r="A17" s="17" t="n"/>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="A17" s="24" t="n"/>
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>15:30-17:00
 Français
@@ -3827,13 +3807,13 @@
       </c>
     </row>
     <row r="18" ht="63" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>9éme (B)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>19:15-20:45
 SVT
@@ -3847,16 +3827,16 @@
 Yahya</t>
         </is>
       </c>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>17:30-19:00
 Math
 Hajer</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr">
         <is>
           <t>09:00-10:30
 Anglais
@@ -3865,14 +3845,14 @@
       </c>
     </row>
     <row r="19" ht="63" customHeight="1">
-      <c r="A19" s="17" t="n"/>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="A19" s="24" t="n"/>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="13" t="inlineStr">
         <is>
           <t>17:00-18:30
 Français
@@ -3881,21 +3861,21 @@
       </c>
     </row>
     <row r="20" ht="63" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>9éme (C)</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>19:30-21:00
 Anglais
@@ -3909,51 +3889,51 @@
 Yahya</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>19:00-20:30
 Math
 Hajer</t>
         </is>
       </c>
-      <c r="H20" s="12" t="n"/>
+      <c r="H20" s="17" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>CYCLE SECONDAIRE   (8 classes)</t>
         </is>
       </c>
-      <c r="B21" s="19" t="n"/>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="19" t="n"/>
-      <c r="F21" s="19" t="n"/>
-      <c r="G21" s="19" t="n"/>
-      <c r="H21" s="19" t="n"/>
+      <c r="B21" s="26" t="n"/>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="26" t="n"/>
+      <c r="E21" s="26" t="n"/>
+      <c r="F21" s="26" t="n"/>
+      <c r="G21" s="26" t="n"/>
+      <c r="H21" s="26" t="n"/>
     </row>
     <row r="22" ht="63" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>1ére (A)</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>19:15-20:45
 Français
 Nassima</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
       <c r="F22" s="10" t="inlineStr">
         <is>
           <t>17:30-19:00
@@ -3961,8 +3941,8 @@
 Najet</t>
         </is>
       </c>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>09:00-10:30
 Physique
@@ -3971,27 +3951,27 @@
       </c>
     </row>
     <row r="23" ht="63" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>1ére (B)</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>19:15-20:45
 Français
 Nassima</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>19:15-20:45 Q-B
 Anglais
@@ -4005,8 +3985,8 @@
 Najet</t>
         </is>
       </c>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>10:30-12:00
 Physique
@@ -4015,14 +3995,14 @@
       </c>
     </row>
     <row r="24" ht="63" customHeight="1">
-      <c r="A24" s="17" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>13:00-14:30 Q-B
 SVT
@@ -4031,12 +4011,12 @@
       </c>
     </row>
     <row r="25" ht="63" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>2éme Eco</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
+      <c r="B25" s="11" t="n"/>
       <c r="C25" s="10" t="inlineStr">
         <is>
           <t>19:30-21:00 Q-B
@@ -4044,29 +4024,29 @@
 Najet</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="28" t="inlineStr">
         <is>
           <t>19:00-20:30
 Gestion
 Yassine</t>
         </is>
       </c>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="29" t="inlineStr">
         <is>
           <t>15:30-17:00 Q-B
 Géographie
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="30" t="inlineStr">
         <is>
           <t>09:00-10:30
 Eco
@@ -4075,30 +4055,30 @@
       </c>
     </row>
     <row r="26" ht="63" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>2éme SCE</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>16:00-17:30
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>12:00-13:30
 Physique
@@ -4107,80 +4087,80 @@
       </c>
     </row>
     <row r="27" ht="63" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>2éme INFO</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="31" t="inlineStr">
         <is>
           <t>17:00-19:00
 Informatique
 Aymen</t>
         </is>
       </c>
-      <c r="H27" s="11" t="n"/>
+      <c r="H27" s="14" t="n"/>
     </row>
     <row r="28" ht="63" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>3éme Eco</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="32" t="inlineStr">
         <is>
           <t>19:15-20:45 Q-B OPT
 Espagnol
 Imen</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="28" t="inlineStr">
         <is>
           <t>19:00-20:30
 Gestion
 Yassine</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>19:00-20:30 Q-B
 Philo
 Fayssel</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>17:30-19:00 Q-B
 Anglais
 Khaled</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="29" t="inlineStr">
         <is>
           <t>17:00-18:30 Q-B
 Géographie
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="30" t="inlineStr">
         <is>
           <t>10:30-12:00
 Eco
@@ -4189,14 +4169,14 @@
       </c>
     </row>
     <row r="29" ht="63" customHeight="1">
-      <c r="A29" s="17" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="A29" s="24" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>14:00-15:30
 Math
@@ -4205,36 +4185,36 @@
       </c>
     </row>
     <row r="30" ht="63" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>3éme INFO</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="34" t="inlineStr">
         <is>
           <t>15:30-17:30
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="35" t="inlineStr">
         <is>
           <t>15:00-17:00
 ALGO
 Aymen</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>12:00-13:30
 Math
@@ -4243,46 +4223,46 @@
       </c>
     </row>
     <row r="31" ht="63" customHeight="1">
-      <c r="A31" s="17" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="A31" s="24" t="n"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>19:15-20:45 Q-B OPT
 Italien
 Amel</t>
         </is>
       </c>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="23" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
     </row>
     <row r="32" ht="63" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>3éme SCE</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>19:00-20:30
 Math
 Lotfi</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n"/>
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>17:30-19:00
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>10:30-12:00
 Physique
@@ -4291,34 +4271,34 @@
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="37" t="inlineStr">
         <is>
           <t>CYCLE BAC   (3 classes)</t>
         </is>
       </c>
-      <c r="B33" s="22" t="n"/>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="22" t="n"/>
-      <c r="E33" s="22" t="n"/>
-      <c r="F33" s="22" t="n"/>
-      <c r="G33" s="22" t="n"/>
-      <c r="H33" s="22" t="n"/>
+      <c r="B33" s="38" t="n"/>
+      <c r="C33" s="38" t="n"/>
+      <c r="D33" s="38" t="n"/>
+      <c r="E33" s="38" t="n"/>
+      <c r="F33" s="38" t="n"/>
+      <c r="G33" s="38" t="n"/>
+      <c r="H33" s="38" t="n"/>
     </row>
     <row r="34" ht="63" customHeight="1">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="39" t="inlineStr">
         <is>
           <t>Bac Eco</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>19:00-21:00
 Gestion
 Yassine</t>
         </is>
       </c>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
       <c r="E34" s="10" t="inlineStr">
         <is>
           <t>19:30-21:00 Q-B
@@ -4326,21 +4306,21 @@
 Najet</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>17:30-19:00 Q-B
 Français
 Nabil</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="29" t="inlineStr">
         <is>
           <t>18:30-20:00 Q-B
 Géographie
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>10:30-12:00
 Math
@@ -4349,14 +4329,14 @@
       </c>
     </row>
     <row r="35" ht="63" customHeight="1">
-      <c r="A35" s="17" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="A35" s="24" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="14" t="n"/>
+      <c r="H35" s="30" t="inlineStr">
         <is>
           <t>12:30-14:30
 Eco
@@ -4365,68 +4345,68 @@
       </c>
     </row>
     <row r="36" ht="63" customHeight="1">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="A36" s="39" t="inlineStr">
         <is>
           <t>Bac SCE</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>19:00-21:00
 Physique
 Sondes</t>
         </is>
       </c>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 Math
 Ahmed</t>
         </is>
       </c>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="E36" s="23" t="n"/>
+      <c r="F36" s="23" t="n"/>
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>19:00-20:30
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H36" s="11" t="n"/>
+      <c r="H36" s="14" t="n"/>
     </row>
     <row r="37" ht="63" customHeight="1">
-      <c r="A37" s="23" t="inlineStr">
+      <c r="A37" s="39" t="inlineStr">
         <is>
           <t>Bac INFO</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="34" t="inlineStr">
         <is>
           <t>19:00-21:00
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
+      <c r="G37" s="35" t="inlineStr">
         <is>
           <t>19:00-21:00
 ALGO
 Heni</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>15:30-17:00
 Math
@@ -4465,58 +4445,22 @@
   </mergeCells>
   <conditionalFormatting sqref="B5:H37">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Math"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"رياضيات"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Annulé",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Physique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"فيزياء"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Examen / Devoir",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Français"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Rattrapage",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Arabe"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"عربية"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ À confirmer",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Anglais"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Changement de salle",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="5" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"SVT"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="7" dxfId="6" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Éveil scientifique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"إيقاظ علمي"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="8" dxfId="7" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Histoire"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Géographie"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="10" dxfId="9" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Philo"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="11" dxfId="10" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Eco"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="12" dxfId="11" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Gestion"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="13" dxfId="12" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Informatique"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="14" dxfId="13" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"ALGO"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="15" dxfId="14" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"STI"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="16" dxfId="15" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Espagnol"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="17" dxfId="16" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Italien"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="18" dxfId="17" stopIfTrue="1">
-      <formula>LEN(B5)=0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Séance en ligne",B5))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1" gridLines="0"/>
@@ -4575,7 +4519,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Une case = une séance : horaire / matière / enseignant.   Chaque matière a sa couleur.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.</t>
+          <t>Une case = une séance : horaire / matière / enseignant.   Chaque matière a sa couleur.   Une case fusionnée sur plusieurs classes = séance commune à ces groupes.   Q-A ou Q-B = une semaine sur deux.   OPT = cours au choix.   Les couleurs sont modifiables à la main ; seul un statut ⚑ les remplace.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4662,30 +4606,30 @@
 Lobna</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 رياضيات
 Bassma</t>
         </is>
       </c>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>19:00-20:30 Q-A
 إيقاظ علمي
 Bassma</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>16:00-17:30
 Français
 Hend</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t>10:30-12:00 Q-A
 Anglais
@@ -4699,7 +4643,7 @@
           <t>5éme</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n"/>
+      <c r="B7" s="11" t="n"/>
       <c r="C7" s="10" t="inlineStr">
         <is>
           <t>19:00-21:00
@@ -4707,23 +4651,23 @@
 Lobna</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 رياضيات
 Bassma</t>
         </is>
       </c>
-      <c r="F7" s="10" t="n"/>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>18:00-19:30
 Français
 Hend</t>
         </is>
       </c>
-      <c r="H7" s="11" t="n"/>
+      <c r="H7" s="14" t="n"/>
     </row>
     <row r="8" ht="63" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -4731,37 +4675,37 @@
           <t>6éme Pilote (A)</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>19:00-20:30
 Français
 Hend</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 رياضيات
 Noura</t>
         </is>
       </c>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>19:30-21:00
 إيقاظ علمي
 Noura</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>19:00-21:00
 عربية
 Lobna</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>12:00-13:30 Q-A
 Anglais
@@ -4775,83 +4719,83 @@
           <t>6éme (B)</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>19:00-20:30
 Français
 Hend</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 رياضيات
 Noura</t>
         </is>
       </c>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>17:00-19:00
 عربية
 Lobna</t>
         </is>
       </c>
-      <c r="H9" s="12" t="n"/>
+      <c r="H9" s="17" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>CYCLE COLLÈGE   (8 classes)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="14" t="n"/>
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
     </row>
     <row r="11" ht="63" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>7éme (A)</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>19:00-20:30 Q-A
 Anglais
 Imen Ben Lazrak</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 فيزياء
 Melek</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>18:00-19:30
 Math
 Khouloud</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>16:00-17:30 Q-A
 SVT
 Sabrine</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>14:00-15:30
 Français
@@ -4860,23 +4804,23 @@
       </c>
     </row>
     <row r="12" ht="63" customHeight="1">
-      <c r="A12" s="17" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="A12" s="24" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>18:00-19:30
 Arabe
 Awatef</t>
         </is>
       </c>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="14" t="n"/>
     </row>
     <row r="13" ht="63" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>7éme (B)</t>
         </is>
@@ -4888,18 +4832,18 @@
 Yahya</t>
         </is>
       </c>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Khouloud</t>
         </is>
       </c>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t>15:30-17:00
 Français
@@ -4908,13 +4852,13 @@
       </c>
     </row>
     <row r="14" ht="63" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>8éme (A)</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
       <c r="D14" s="10" t="inlineStr">
         <is>
           <t>19:00-20:30
@@ -4922,28 +4866,28 @@
 Awatef</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>19:15-20:45
 Français
 Nassima</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 فيزياء
 Melek</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>17:30-19:00 Q-A
 SVT
 Sabrine</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>13:45-15:15
 Math
@@ -4952,12 +4896,12 @@
       </c>
     </row>
     <row r="15" ht="63" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>8éme (B)</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n"/>
+      <c r="B15" s="11" t="n"/>
       <c r="C15" s="10" t="inlineStr">
         <is>
           <t>19:30-21:00
@@ -4965,23 +4909,23 @@
 Yahya</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>19:15-20:45
 Math
 Khouloud</t>
         </is>
       </c>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>17:30-19:00 Q-A
 Anglais
 Imen Ben Lazrak</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t>17:00-18:30
 Français
@@ -4990,68 +4934,68 @@
       </c>
     </row>
     <row r="16" ht="63" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>8éme (C)</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>19:30-21:00
 Français
 Nabil</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>19:15-20:45
 Math
 Khouloud</t>
         </is>
       </c>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="11" t="n"/>
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="14" t="n"/>
     </row>
     <row r="17" ht="63" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>9éme (A)</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 فيزياء
 Melek</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>19:00-20:30
 Math
 Faouzi</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
       </c>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>16:30-18:00
 Arabe
 Awatef</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>10:30-12:00
 Anglais
@@ -5060,14 +5004,14 @@
       </c>
     </row>
     <row r="18" ht="63" customHeight="1">
-      <c r="A18" s="17" t="n"/>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="A18" s="24" t="n"/>
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t>15:30-17:00
 Français
@@ -5076,13 +5020,13 @@
       </c>
     </row>
     <row r="19" ht="63" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>9éme (B)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>19:15-20:45
 SVT
@@ -5096,16 +5040,16 @@
 Yahya</t>
         </is>
       </c>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>17:30-19:00
 Math
 Hajer</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>09:00-10:30
 Anglais
@@ -5114,14 +5058,14 @@
       </c>
     </row>
     <row r="20" ht="63" customHeight="1">
-      <c r="A20" s="17" t="n"/>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="A20" s="24" t="n"/>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="13" t="inlineStr">
         <is>
           <t>17:00-18:30
 Français
@@ -5130,21 +5074,21 @@
       </c>
     </row>
     <row r="21" ht="63" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>9éme (C)</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>19:15-20:45
 SVT
 Imen Jribi</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>19:30-21:00
 Anglais
@@ -5158,51 +5102,51 @@
 Yahya</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>19:00-20:30
 Math
 Hajer</t>
         </is>
       </c>
-      <c r="H21" s="12" t="n"/>
+      <c r="H21" s="17" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>CYCLE SECONDAIRE   (8 classes)</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="19" t="n"/>
-      <c r="F22" s="19" t="n"/>
-      <c r="G22" s="19" t="n"/>
-      <c r="H22" s="19" t="n"/>
+      <c r="B22" s="26" t="n"/>
+      <c r="C22" s="26" t="n"/>
+      <c r="D22" s="26" t="n"/>
+      <c r="E22" s="26" t="n"/>
+      <c r="F22" s="26" t="n"/>
+      <c r="G22" s="26" t="n"/>
+      <c r="H22" s="26" t="n"/>
     </row>
     <row r="23" ht="63" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>1ére (A)</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>19:15-20:45
 Français
 Nassima</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>19:15-20:45 Q-A
 Anglais
@@ -5216,8 +5160,8 @@
 Najet</t>
         </is>
       </c>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>09:00-10:30
 Physique
@@ -5226,14 +5170,14 @@
       </c>
     </row>
     <row r="24" ht="63" customHeight="1">
-      <c r="A24" s="17" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>13:00-14:30 Q-A
 SVT
@@ -5242,27 +5186,27 @@
       </c>
     </row>
     <row r="25" ht="63" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>1ére (B)</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>19:15-20:45
 Français
 Nassima</t>
         </is>
       </c>
-      <c r="E25" s="10" t="n"/>
+      <c r="E25" s="11" t="n"/>
       <c r="F25" s="10" t="inlineStr">
         <is>
           <t>19:00-20:30
@@ -5270,8 +5214,8 @@
 Najet</t>
         </is>
       </c>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>10:30-12:00
 Physique
@@ -5280,48 +5224,48 @@
       </c>
     </row>
     <row r="26" ht="63" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>2éme Eco</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>19:15-20:45 Q-A
 Anglais
 Imen Bennour</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="28" t="inlineStr">
         <is>
           <t>19:00-20:30
 Gestion
 Yassine</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>17:30-19:00 Q-A
 Français
 Nabil</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="40" t="inlineStr">
         <is>
           <t>15:30-17:00 Q-A
 Histoire
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="30" t="inlineStr">
         <is>
           <t>09:00-10:30
 Eco
@@ -5330,30 +5274,30 @@
       </c>
     </row>
     <row r="27" ht="63" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>2éme SCE</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="F27" s="16" t="n"/>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>16:00-17:30
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>12:00-13:30
 Physique
@@ -5362,56 +5306,56 @@
       </c>
     </row>
     <row r="28" ht="63" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>2éme INFO</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="31" t="inlineStr">
         <is>
           <t>17:00-19:00
 Informatique
 Aymen</t>
         </is>
       </c>
-      <c r="H28" s="11" t="n"/>
+      <c r="H28" s="14" t="n"/>
     </row>
     <row r="29" ht="63" customHeight="1">
-      <c r="A29" s="17" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="A29" s="24" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>19:30-21:00
 Math
 Haythem</t>
         </is>
       </c>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="14" t="n"/>
     </row>
     <row r="30" ht="63" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>3éme Eco</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="28" t="inlineStr">
         <is>
           <t>19:00-20:30
 Gestion
@@ -5425,21 +5369,21 @@
 Najet</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>19:00-20:30 Q-A
 Français
 Nabil</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="40" t="inlineStr">
         <is>
           <t>17:00-18:30 Q-A
 Histoire
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="30" t="inlineStr">
         <is>
           <t>10:30-12:00
 Eco
@@ -5448,14 +5392,14 @@
       </c>
     </row>
     <row r="31" ht="63" customHeight="1">
-      <c r="A31" s="17" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="A31" s="24" t="n"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="23" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>14:00-15:30
 Math
@@ -5464,36 +5408,36 @@
       </c>
     </row>
     <row r="32" ht="63" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>3éme INFO</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="34" t="inlineStr">
         <is>
           <t>15:30-17:30
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="E32" s="23" t="n"/>
+      <c r="F32" s="23" t="n"/>
+      <c r="G32" s="35" t="inlineStr">
         <is>
           <t>15:00-17:00
 ALGO
 Aymen</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>12:00-13:30
 Math
@@ -5502,30 +5446,30 @@
       </c>
     </row>
     <row r="33" ht="63" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>3éme SCE</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>19:00-20:30
 Math
 Lotfi</t>
         </is>
       </c>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="12" t="n"/>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>17:30-19:00
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>10:30-12:00
 Physique
@@ -5534,62 +5478,62 @@
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="37" t="inlineStr">
         <is>
           <t>CYCLE BAC   (3 classes)</t>
         </is>
       </c>
-      <c r="B34" s="22" t="n"/>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="22" t="n"/>
-      <c r="E34" s="22" t="n"/>
-      <c r="F34" s="22" t="n"/>
-      <c r="G34" s="22" t="n"/>
-      <c r="H34" s="22" t="n"/>
+      <c r="B34" s="38" t="n"/>
+      <c r="C34" s="38" t="n"/>
+      <c r="D34" s="38" t="n"/>
+      <c r="E34" s="38" t="n"/>
+      <c r="F34" s="38" t="n"/>
+      <c r="G34" s="38" t="n"/>
+      <c r="H34" s="38" t="n"/>
     </row>
     <row r="35" ht="63" customHeight="1">
-      <c r="A35" s="23" t="inlineStr">
+      <c r="A35" s="39" t="inlineStr">
         <is>
           <t>Bac Eco</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>19:00-21:00
 Gestion
 Yassine</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C35" s="32" t="inlineStr">
         <is>
           <t>19:15-20:45 Q-A OPT
 Espagnol
 Imen</t>
         </is>
       </c>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="33" t="inlineStr">
         <is>
           <t>19:00-20:30 Q-A
 Philo
 Fayssel</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>17:30-19:00 Q-A
 Anglais
 Khaled</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G35" s="40" t="inlineStr">
         <is>
           <t>18:30-20:00 Q-A
 Histoire
 Abdelwaheb</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>10:30-12:00
 Math
@@ -5598,14 +5542,14 @@
       </c>
     </row>
     <row r="36" ht="63" customHeight="1">
-      <c r="A36" s="17" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="A36" s="24" t="n"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="23" t="n"/>
+      <c r="F36" s="23" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="30" t="inlineStr">
         <is>
           <t>12:30-14:30
 Eco
@@ -5614,84 +5558,84 @@
       </c>
     </row>
     <row r="37" ht="63" customHeight="1">
-      <c r="A37" s="23" t="inlineStr">
+      <c r="A37" s="39" t="inlineStr">
         <is>
           <t>Bac SCE</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>19:00-21:00
 Physique
 Sondes</t>
         </is>
       </c>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>19:00-21:00
 Math
 Ahmed</t>
         </is>
       </c>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="E37" s="23" t="n"/>
+      <c r="F37" s="23" t="n"/>
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>19:00-20:30
 SVT
 Rym</t>
         </is>
       </c>
-      <c r="H37" s="11" t="n"/>
+      <c r="H37" s="14" t="n"/>
     </row>
     <row r="38" ht="63" customHeight="1">
-      <c r="A38" s="17" t="n"/>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="A38" s="24" t="n"/>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="36" t="inlineStr">
         <is>
           <t>19:15-20:45 Q-A OPT
 Italien
 Amel</t>
         </is>
       </c>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
-      <c r="G38" s="11" t="n"/>
-      <c r="H38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="23" t="n"/>
+      <c r="F38" s="23" t="n"/>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="14" t="n"/>
     </row>
     <row r="39" ht="63" customHeight="1">
-      <c r="A39" s="23" t="inlineStr">
+      <c r="A39" s="39" t="inlineStr">
         <is>
           <t>Bac INFO</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>19:30-21:00
 Physique
 Samia</t>
         </is>
       </c>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="34" t="inlineStr">
         <is>
           <t>19:00-21:00
 STI
 Aymen</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n"/>
-      <c r="F39" s="12" t="n"/>
-      <c r="G39" s="11" t="inlineStr">
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
+      <c r="G39" s="35" t="inlineStr">
         <is>
           <t>19:00-21:00
 ALGO
 Heni</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>15:30-17:00
 Math
@@ -5734,58 +5678,22 @@
   </mergeCells>
   <conditionalFormatting sqref="B5:H39">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Math"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"رياضيات"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Annulé",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Physique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"فيزياء"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Examen / Devoir",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Français"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Rattrapage",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Arabe"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"عربية"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ À confirmer",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Anglais"&amp;CHAR(10),B5)))&gt;0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Changement de salle",B5))</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="5" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"SVT"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="7" dxfId="6" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Éveil scientifique"&amp;CHAR(10),B5))+ISNUMBER(SEARCH(CHAR(10)&amp;"إيقاظ علمي"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="8" dxfId="7" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Histoire"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Géographie"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="10" dxfId="9" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Philo"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="11" dxfId="10" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Eco"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="12" dxfId="11" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Gestion"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="13" dxfId="12" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Informatique"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="14" dxfId="13" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"ALGO"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="15" dxfId="14" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"STI"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="16" dxfId="15" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Espagnol"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="17" dxfId="16" stopIfTrue="1">
-      <formula>(ISNUMBER(SEARCH(CHAR(10)&amp;"Italien"&amp;CHAR(10),B5)))&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="18" dxfId="17" stopIfTrue="1">
-      <formula>LEN(B5)=0</formula>
+      <formula>ISNUMBER(SEARCH("⚑ Séance en ligne",B5))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1" gridLines="0"/>
